--- a/GATEWAY/A1_111_DLABSRLXX/D.Lab_Srl/OsteoEasy/2.0/report-checklist.xlsx
+++ b/GATEWAY/A1_111_DLABSRLXX/D.Lab_Srl/OsteoEasy/2.0/report-checklist.xlsx
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="688">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="690">
   <si>
     <t>COME VALORIZZARE LA CHECKLIST (tab TestCases)</t>
   </si>
@@ -390,10 +390,13 @@
     <t>VALIDAZIONE_TOKEN_JWT_RSA_KO</t>
   </si>
   <si>
-    <t>01/04/2026</t>
-  </si>
-  <si>
-    <t>2026-04-01T16:51:28+02:00</t>
+    <t>03/04/2026</t>
+  </si>
+  <si>
+    <t>2026-04-03T08:55:57+02:00</t>
+  </si>
+  <si>
+    <t>e4cbe928d3367379bb29becc62b6a271</t>
   </si>
   <si>
     <t>SI</t>
@@ -492,7 +495,7 @@
     <t>VALIDAZIONE_TOKEN_JWT_CAMPO_RSA_KO</t>
   </si>
   <si>
-    <t>0e0b20464dc30dd05dc98bac753aaeb0</t>
+    <t>16dbcf2db05f5d236691d07bf272b2c6</t>
   </si>
   <si>
     <t>VALIDAZIONE_TOKEN_JWT_CAMPO_CERT_VAC_KO</t>
@@ -1112,10 +1115,13 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 6" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>2aac42bcb604098b3d2366df7299a23b</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.dd9cdec9fe^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>2026-04-03T08:55:58+02:00</t>
+  </si>
+  <si>
+    <t>f3e8211741752326f40bcc70611a5d7d</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.eab7ea2a56^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>Si e' verificato un errore durante l'operazione. Errore di validazione del documento CDA. Verificare il contenuto del documento e riprovare.</t>
@@ -1131,13 +1137,10 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 8" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>2026-04-01T16:51:29+02:00</t>
-  </si>
-  <si>
-    <t>91021ec5e7bb4c151116608e8a726582</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.4b2aea34e0^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>6290482be6ab3944900a533193ed8abf</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.771763e932^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RSA_CT9_KO</t>
@@ -1147,10 +1150,10 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 9" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>8dfd0065669f00fb6caf5b967e830f95</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.7192636754^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>8925a9a26e0f147bde4d645f633ddead</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.3bb4251d43^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RSA_CT10_KO</t>
@@ -1160,10 +1163,10 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 10" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>ea37cf705143974269aee26cb808a00b</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.0cbe10b46b^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>f957e6203e3bc87af35179f4b13dc90e</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.bbb899b1de^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RSA_CT13_KO</t>
@@ -1173,13 +1176,13 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 13" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>2026-04-01T16:51:30+02:00</t>
-  </si>
-  <si>
-    <t>9ef9294e7b475418402e38eb3947df89</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.3b6353ddd1^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>2026-04-03T08:55:59+02:00</t>
+  </si>
+  <si>
+    <t>0771b01e0f1fb116377ee9fabd753bbe</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.186999bd77^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RSA_CT14_KO</t>
@@ -1189,10 +1192,10 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 14" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>0828ae2932439e8ac2518d1405ac239c</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.85c6b9c655^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>a963b22cd7cde9192710f6d264da436d</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.f952ed1f3c^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RSA_CT15_KO</t>
@@ -1202,10 +1205,10 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 15" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>857a73493f9ec068dd7f3d238dae3a6f</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.77428174eb^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>c356c36d9fbab67b3c3dd59843b44948</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.708f92b7c0^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RSA_CT16_KO</t>
@@ -1215,10 +1218,13 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 16" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>6b2ca9c0349a2e740debb0c9d49cdbce</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.7b750c9cf4^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>2026-04-03T08:56:00+02:00</t>
+  </si>
+  <si>
+    <t>0fe3f7b3e99b578acb7586a39b845750</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.8127a1416d^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RSA_CT17_KO</t>
@@ -1228,13 +1234,10 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 17" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>2026-04-01T16:51:31+02:00</t>
-  </si>
-  <si>
-    <t>fc26fc824f964e4f3302af1197b19cea</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.ff4fa5b613^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>84297aec955c9eeb4c911ae6ee49f45c</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.8517eaadda^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RSA_CT18_KO</t>
@@ -1244,10 +1247,10 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 18" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>99840002cb527779d4167215430e51c0</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.165c2344e9^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>e7c274eb375320ce00e905f6fd2e1179</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.947422b0bd^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RSA_CT19_KO</t>
@@ -1257,10 +1260,10 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 19" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>87f13ffc15fd5a6f27a8be32757cd287</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.41fb17bb36^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>26c5d1b3e06dd6238ab65cc62efa212a</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.3f1f3284c9^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RSA_CT20_KO</t>
@@ -1270,10 +1273,13 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 20" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>4c938bc66b069da4ae3c76f0189c2b12</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.7c8dd54190^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>2026-04-03T08:56:01+02:00</t>
+  </si>
+  <si>
+    <t>4c1d170ce7f35b229c164970faa70921</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.641ed129c1^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RSA_CT21_KO</t>
@@ -1283,10 +1289,10 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 21" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>20bd27b6e11a07cb06505ae160926a7a</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.a359fc981d^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>dd1dab393f5514349139f284b880a281</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.98cae7d745^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RSA_CT22_KO</t>
@@ -1296,13 +1302,10 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 22" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>2026-04-01T16:51:32+02:00</t>
-  </si>
-  <si>
-    <t>9ab461fc8828fe6c6178b4c74973be79</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.750d115faa^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>b4f2807e75d2cdd87b1ddb9b99ac29cd</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.8dca82b5dc^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RSA_CT23_KO</t>
@@ -1312,10 +1315,13 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 23" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>507b43042d6ce30da2e3975828f219cd</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.7b33617417^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>2026-04-03T08:56:02+02:00</t>
+  </si>
+  <si>
+    <t>4b4225c36393a2fde7ed1636fcd97d9d</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.4bb3c6cbab^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_PSS_CT6_KO</t>
@@ -1555,10 +1561,10 @@
 Il Documento CDA2 Referto Specialistica Ambulatoriale dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 24" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>554ff83b9a81571e8a0ecd6a8f8cb02e</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.54ff36d26a^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>9fc297b462711c6a0c93e0c394ac55bf</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.559394b32c^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RSA_CT25</t>
@@ -1568,10 +1574,10 @@
 Il Documento CDA2 Referto Specialistica Ambulatoriale dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 25" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>4041a75aec43573a3bf6ad72fb172c20</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.f41606600b^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>1c975a5d8d21a09f2fd72b0a1b1d84fd</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.12aad0cbef^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_LDO_CT17</t>
@@ -1652,13 +1658,10 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 26" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>2026-04-01T16:51:33+02:00</t>
-  </si>
-  <si>
-    <t>170d499510ab9641f1bd5dbf1cbebe6f</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.45c0d55039^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>b418b517cbc0940ea77bd83e0012149b</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.29b5acc539^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RAD_CT24_KO</t>
@@ -1710,7 +1713,7 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 27" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>e22f54bc7cffc0d64466e1a4281661fd</t>
+    <t>af819f8409c307f6c87a1bcbf6fe25d3</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_PSS_CT22_KO</t>
@@ -1762,10 +1765,13 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 28" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>933d3e852f494c4f7830f6f2953ff91d</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.ac047efc72^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>2026-04-03T08:56:03+02:00</t>
+  </si>
+  <si>
+    <t>b1d4cdb3427cb7d71bd542bc5c93ee3c</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.6a844f08ee^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_PSS_CT23</t>
@@ -5166,33 +5172,35 @@
       <c r="G15" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="H15" s="31"/>
+      <c r="H15" s="31" t="s">
+        <v>69</v>
+      </c>
       <c r="I15" s="36"/>
       <c r="J15" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K15" s="32"/>
       <c r="L15" s="32"/>
       <c r="M15" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N15" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O15" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="P15" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q15" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="R15" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="P15" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q15" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="R15" s="32" t="s">
-        <v>69</v>
-      </c>
       <c r="S15" s="32" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T15" s="32"/>
       <c r="U15" s="33"/>
@@ -5209,10 +5217,10 @@
         <v>49</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" s="29" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E16" s="37" t="s">
         <v>57</v>
@@ -5250,10 +5258,10 @@
         <v>49</v>
       </c>
       <c r="C17" s="35" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D17" s="29" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E17" s="37" t="s">
         <v>57</v>
@@ -5291,10 +5299,10 @@
         <v>49</v>
       </c>
       <c r="C18" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D18" s="29" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E18" s="37" t="s">
         <v>57</v>
@@ -5335,10 +5343,10 @@
         <v>50</v>
       </c>
       <c r="D19" s="29" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E19" s="37" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F19" s="31"/>
       <c r="G19" s="31"/>
@@ -5376,10 +5384,10 @@
         <v>59</v>
       </c>
       <c r="D20" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="E20" s="37" t="s">
         <v>80</v>
-      </c>
-      <c r="E20" s="37" t="s">
-        <v>79</v>
       </c>
       <c r="F20" s="31"/>
       <c r="G20" s="31"/>
@@ -5417,10 +5425,10 @@
         <v>61</v>
       </c>
       <c r="D21" s="29" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E21" s="37" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F21" s="31"/>
       <c r="G21" s="31"/>
@@ -5458,10 +5466,10 @@
         <v>63</v>
       </c>
       <c r="D22" s="29" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E22" s="37" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F22" s="31"/>
       <c r="G22" s="31"/>
@@ -5499,10 +5507,10 @@
         <v>65</v>
       </c>
       <c r="D23" s="29" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E23" s="37" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F23" s="31" t="s">
         <v>67</v>
@@ -5511,34 +5519,34 @@
         <v>68</v>
       </c>
       <c r="H23" s="31" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I23" s="36"/>
       <c r="J23" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K23" s="32"/>
       <c r="L23" s="32"/>
       <c r="M23" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N23" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O23" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="P23" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q23" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="R23" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="P23" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q23" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="R23" s="32" t="s">
-        <v>69</v>
-      </c>
       <c r="S23" s="32" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T23" s="32"/>
       <c r="U23" s="33"/>
@@ -5555,13 +5563,13 @@
         <v>49</v>
       </c>
       <c r="C24" s="35" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D24" s="29" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E24" s="37" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F24" s="31"/>
       <c r="G24" s="31"/>
@@ -5596,13 +5604,13 @@
         <v>49</v>
       </c>
       <c r="C25" s="35" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D25" s="29" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E25" s="37" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F25" s="31"/>
       <c r="G25" s="31"/>
@@ -5637,13 +5645,13 @@
         <v>49</v>
       </c>
       <c r="C26" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D26" s="29" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E26" s="37" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F26" s="31"/>
       <c r="G26" s="31"/>
@@ -5681,10 +5689,10 @@
         <v>50</v>
       </c>
       <c r="D27" s="29" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E27" s="37" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F27" s="31"/>
       <c r="G27" s="31"/>
@@ -5706,7 +5714,7 @@
       <c r="S27" s="32"/>
       <c r="T27" s="32"/>
       <c r="U27" s="33" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="V27" s="34"/>
       <c r="W27" s="32" t="s">
@@ -5724,10 +5732,10 @@
         <v>59</v>
       </c>
       <c r="D28" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="E28" s="37" t="s">
         <v>90</v>
-      </c>
-      <c r="E28" s="37" t="s">
-        <v>89</v>
       </c>
       <c r="F28" s="31"/>
       <c r="G28" s="31"/>
@@ -5749,7 +5757,7 @@
       <c r="S28" s="32"/>
       <c r="T28" s="32"/>
       <c r="U28" s="33" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="V28" s="34"/>
       <c r="W28" s="32" t="s">
@@ -5767,10 +5775,10 @@
         <v>61</v>
       </c>
       <c r="D29" s="29" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E29" s="37" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F29" s="31"/>
       <c r="G29" s="31"/>
@@ -5792,7 +5800,7 @@
       <c r="S29" s="32"/>
       <c r="T29" s="32"/>
       <c r="U29" s="33" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="V29" s="34"/>
       <c r="W29" s="32" t="s">
@@ -5810,10 +5818,10 @@
         <v>63</v>
       </c>
       <c r="D30" s="29" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E30" s="37" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F30" s="31"/>
       <c r="G30" s="31"/>
@@ -5835,7 +5843,7 @@
       <c r="S30" s="32"/>
       <c r="T30" s="32"/>
       <c r="U30" s="33" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="V30" s="34"/>
       <c r="W30" s="32" t="s">
@@ -5853,32 +5861,28 @@
         <v>65</v>
       </c>
       <c r="D31" s="29" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E31" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="F31" s="31" t="s">
-        <v>67</v>
-      </c>
-      <c r="G31" s="31" t="s">
-        <v>68</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="F31" s="31"/>
+      <c r="G31" s="31"/>
       <c r="H31" s="31"/>
       <c r="I31" s="36"/>
       <c r="J31" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K31" s="32"/>
       <c r="L31" s="32"/>
       <c r="M31" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N31" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O31" s="32" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P31" s="32" t="s">
         <v>53</v>
@@ -5887,14 +5891,14 @@
         <v>53</v>
       </c>
       <c r="R31" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="S31" s="32" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T31" s="32"/>
       <c r="U31" s="33" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="V31" s="34"/>
       <c r="W31" s="32" t="s">
@@ -5909,13 +5913,13 @@
         <v>49</v>
       </c>
       <c r="C32" s="35" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D32" s="29" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E32" s="37" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F32" s="31"/>
       <c r="G32" s="31"/>
@@ -5937,7 +5941,7 @@
       <c r="S32" s="32"/>
       <c r="T32" s="32"/>
       <c r="U32" s="33" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="V32" s="34"/>
       <c r="W32" s="32" t="s">
@@ -5952,13 +5956,13 @@
         <v>49</v>
       </c>
       <c r="C33" s="35" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D33" s="29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E33" s="37" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F33" s="31"/>
       <c r="G33" s="31"/>
@@ -5980,7 +5984,7 @@
       <c r="S33" s="32"/>
       <c r="T33" s="32"/>
       <c r="U33" s="33" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="V33" s="34"/>
       <c r="W33" s="32" t="s">
@@ -5995,13 +5999,13 @@
         <v>49</v>
       </c>
       <c r="C34" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D34" s="29" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E34" s="37" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F34" s="31"/>
       <c r="G34" s="31"/>
@@ -6023,7 +6027,7 @@
       <c r="S34" s="32"/>
       <c r="T34" s="32"/>
       <c r="U34" s="33" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="V34" s="34"/>
       <c r="W34" s="32" t="s">
@@ -6041,10 +6045,10 @@
         <v>50</v>
       </c>
       <c r="D35" s="29" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E35" s="37" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F35" s="31"/>
       <c r="G35" s="31"/>
@@ -6082,10 +6086,10 @@
         <v>50</v>
       </c>
       <c r="D36" s="29" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E36" s="37" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F36" s="31"/>
       <c r="G36" s="31"/>
@@ -6123,10 +6127,10 @@
         <v>50</v>
       </c>
       <c r="D37" s="29" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E37" s="37" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F37" s="31"/>
       <c r="G37" s="31"/>
@@ -6164,10 +6168,10 @@
         <v>50</v>
       </c>
       <c r="D38" s="29" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E38" s="37" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F38" s="31"/>
       <c r="G38" s="31"/>
@@ -6205,10 +6209,10 @@
         <v>50</v>
       </c>
       <c r="D39" s="29" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E39" s="37" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F39" s="31"/>
       <c r="G39" s="31"/>
@@ -6246,10 +6250,10 @@
         <v>50</v>
       </c>
       <c r="D40" s="29" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E40" s="37" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F40" s="31"/>
       <c r="G40" s="31"/>
@@ -6287,10 +6291,10 @@
         <v>50</v>
       </c>
       <c r="D41" s="29" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E41" s="37" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F41" s="31"/>
       <c r="G41" s="31"/>
@@ -6328,10 +6332,10 @@
         <v>50</v>
       </c>
       <c r="D42" s="29" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E42" s="37" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F42" s="31"/>
       <c r="G42" s="31"/>
@@ -6369,10 +6373,10 @@
         <v>59</v>
       </c>
       <c r="D43" s="29" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E43" s="37" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F43" s="31"/>
       <c r="G43" s="31"/>
@@ -6410,10 +6414,10 @@
         <v>59</v>
       </c>
       <c r="D44" s="29" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E44" s="37" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F44" s="31"/>
       <c r="G44" s="31"/>
@@ -6451,10 +6455,10 @@
         <v>59</v>
       </c>
       <c r="D45" s="29" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E45" s="37" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F45" s="31"/>
       <c r="G45" s="31"/>
@@ -6492,10 +6496,10 @@
         <v>59</v>
       </c>
       <c r="D46" s="29" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E46" s="37" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F46" s="31"/>
       <c r="G46" s="31"/>
@@ -6533,10 +6537,10 @@
         <v>59</v>
       </c>
       <c r="D47" s="29" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E47" s="37" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F47" s="31"/>
       <c r="G47" s="31"/>
@@ -6574,10 +6578,10 @@
         <v>59</v>
       </c>
       <c r="D48" s="29" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E48" s="37" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F48" s="31"/>
       <c r="G48" s="31"/>
@@ -6615,10 +6619,10 @@
         <v>59</v>
       </c>
       <c r="D49" s="29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E49" s="37" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F49" s="31"/>
       <c r="G49" s="31"/>
@@ -6656,10 +6660,10 @@
         <v>59</v>
       </c>
       <c r="D50" s="29" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E50" s="37" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F50" s="31"/>
       <c r="G50" s="31"/>
@@ -6697,10 +6701,10 @@
         <v>59</v>
       </c>
       <c r="D51" s="29" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E51" s="37" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F51" s="31"/>
       <c r="G51" s="31"/>
@@ -6738,10 +6742,10 @@
         <v>59</v>
       </c>
       <c r="D52" s="29" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E52" s="37" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F52" s="31"/>
       <c r="G52" s="31"/>
@@ -6779,10 +6783,10 @@
         <v>63</v>
       </c>
       <c r="D53" s="29" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E53" s="37" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F53" s="31"/>
       <c r="G53" s="31"/>
@@ -6820,10 +6824,10 @@
         <v>63</v>
       </c>
       <c r="D54" s="29" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E54" s="37" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F54" s="31"/>
       <c r="G54" s="31"/>
@@ -6861,10 +6865,10 @@
         <v>63</v>
       </c>
       <c r="D55" s="29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E55" s="37" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F55" s="31"/>
       <c r="G55" s="31"/>
@@ -6902,10 +6906,10 @@
         <v>63</v>
       </c>
       <c r="D56" s="29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E56" s="37" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F56" s="31"/>
       <c r="G56" s="31"/>
@@ -6943,10 +6947,10 @@
         <v>63</v>
       </c>
       <c r="D57" s="29" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E57" s="37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F57" s="31"/>
       <c r="G57" s="31"/>
@@ -6984,10 +6988,10 @@
         <v>63</v>
       </c>
       <c r="D58" s="29" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E58" s="37" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F58" s="31"/>
       <c r="G58" s="31"/>
@@ -7025,10 +7029,10 @@
         <v>63</v>
       </c>
       <c r="D59" s="29" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E59" s="37" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F59" s="31"/>
       <c r="G59" s="31"/>
@@ -7066,10 +7070,10 @@
         <v>63</v>
       </c>
       <c r="D60" s="29" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E60" s="37" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F60" s="31"/>
       <c r="G60" s="31"/>
@@ -7107,10 +7111,10 @@
         <v>63</v>
       </c>
       <c r="D61" s="29" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E61" s="37" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F61" s="31"/>
       <c r="G61" s="31"/>
@@ -7148,10 +7152,10 @@
         <v>63</v>
       </c>
       <c r="D62" s="29" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E62" s="37" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F62" s="31"/>
       <c r="G62" s="31"/>
@@ -7189,10 +7193,10 @@
         <v>63</v>
       </c>
       <c r="D63" s="29" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E63" s="37" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F63" s="31"/>
       <c r="G63" s="31"/>
@@ -7230,10 +7234,10 @@
         <v>63</v>
       </c>
       <c r="D64" s="29" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E64" s="37" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F64" s="31"/>
       <c r="G64" s="31"/>
@@ -7271,10 +7275,10 @@
         <v>63</v>
       </c>
       <c r="D65" s="29" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E65" s="37" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F65" s="31"/>
       <c r="G65" s="31"/>
@@ -7312,10 +7316,10 @@
         <v>63</v>
       </c>
       <c r="D66" s="29" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E66" s="37" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F66" s="31"/>
       <c r="G66" s="31"/>
@@ -7353,10 +7357,10 @@
         <v>63</v>
       </c>
       <c r="D67" s="29" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E67" s="37" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F67" s="31"/>
       <c r="G67" s="31"/>
@@ -7394,10 +7398,10 @@
         <v>63</v>
       </c>
       <c r="D68" s="29" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E68" s="37" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F68" s="31"/>
       <c r="G68" s="31"/>
@@ -7432,13 +7436,13 @@
         <v>49</v>
       </c>
       <c r="C69" s="35" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D69" s="29" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E69" s="37" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F69" s="31"/>
       <c r="G69" s="31"/>
@@ -7473,13 +7477,13 @@
         <v>49</v>
       </c>
       <c r="C70" s="35" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D70" s="29" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E70" s="37" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F70" s="31"/>
       <c r="G70" s="31"/>
@@ -7514,13 +7518,13 @@
         <v>49</v>
       </c>
       <c r="C71" s="35" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D71" s="29" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E71" s="37" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F71" s="31"/>
       <c r="G71" s="31"/>
@@ -7555,13 +7559,13 @@
         <v>49</v>
       </c>
       <c r="C72" s="35" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D72" s="29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E72" s="37" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F72" s="31"/>
       <c r="G72" s="31"/>
@@ -7596,13 +7600,13 @@
         <v>49</v>
       </c>
       <c r="C73" s="35" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D73" s="29" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E73" s="37" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F73" s="31"/>
       <c r="G73" s="31"/>
@@ -7637,13 +7641,13 @@
         <v>49</v>
       </c>
       <c r="C74" s="35" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D74" s="29" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E74" s="37" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F74" s="31"/>
       <c r="G74" s="31"/>
@@ -7678,13 +7682,13 @@
         <v>49</v>
       </c>
       <c r="C75" s="35" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D75" s="29" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E75" s="37" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F75" s="31"/>
       <c r="G75" s="31"/>
@@ -7719,13 +7723,13 @@
         <v>49</v>
       </c>
       <c r="C76" s="35" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D76" s="29" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E76" s="37" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F76" s="31"/>
       <c r="G76" s="31"/>
@@ -7760,13 +7764,13 @@
         <v>49</v>
       </c>
       <c r="C77" s="35" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D77" s="29" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E77" s="37" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F77" s="31"/>
       <c r="G77" s="31"/>
@@ -7801,13 +7805,13 @@
         <v>49</v>
       </c>
       <c r="C78" s="35" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D78" s="29" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E78" s="37" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F78" s="31"/>
       <c r="G78" s="31"/>
@@ -7842,13 +7846,13 @@
         <v>49</v>
       </c>
       <c r="C79" s="35" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D79" s="29" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E79" s="37" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F79" s="31"/>
       <c r="G79" s="31"/>
@@ -7883,13 +7887,13 @@
         <v>49</v>
       </c>
       <c r="C80" s="35" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D80" s="29" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E80" s="37" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F80" s="31"/>
       <c r="G80" s="31"/>
@@ -7924,13 +7928,13 @@
         <v>49</v>
       </c>
       <c r="C81" s="35" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D81" s="29" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E81" s="37" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F81" s="31"/>
       <c r="G81" s="31"/>
@@ -7965,13 +7969,13 @@
         <v>49</v>
       </c>
       <c r="C82" s="35" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D82" s="29" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E82" s="37" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F82" s="31"/>
       <c r="G82" s="31"/>
@@ -8006,13 +8010,13 @@
         <v>49</v>
       </c>
       <c r="C83" s="35" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D83" s="29" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E83" s="37" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F83" s="31"/>
       <c r="G83" s="31"/>
@@ -8047,13 +8051,13 @@
         <v>49</v>
       </c>
       <c r="C84" s="35" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D84" s="29" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E84" s="37" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F84" s="31"/>
       <c r="G84" s="31"/>
@@ -8088,13 +8092,13 @@
         <v>49</v>
       </c>
       <c r="C85" s="35" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D85" s="29" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E85" s="37" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F85" s="31"/>
       <c r="G85" s="31"/>
@@ -8129,13 +8133,13 @@
         <v>49</v>
       </c>
       <c r="C86" s="35" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D86" s="29" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E86" s="37" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F86" s="31"/>
       <c r="G86" s="31"/>
@@ -8170,13 +8174,13 @@
         <v>49</v>
       </c>
       <c r="C87" s="35" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D87" s="29" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E87" s="37" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F87" s="31"/>
       <c r="G87" s="31"/>
@@ -8211,13 +8215,13 @@
         <v>49</v>
       </c>
       <c r="C88" s="35" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D88" s="29" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E88" s="37" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F88" s="31"/>
       <c r="G88" s="31"/>
@@ -8252,13 +8256,13 @@
         <v>49</v>
       </c>
       <c r="C89" s="35" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D89" s="29" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E89" s="37" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F89" s="31"/>
       <c r="G89" s="31"/>
@@ -8293,13 +8297,13 @@
         <v>49</v>
       </c>
       <c r="C90" s="35" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D90" s="29" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E90" s="37" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F90" s="31"/>
       <c r="G90" s="31"/>
@@ -8334,13 +8338,13 @@
         <v>49</v>
       </c>
       <c r="C91" s="35" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D91" s="29" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E91" s="37" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F91" s="31"/>
       <c r="G91" s="31"/>
@@ -8375,13 +8379,13 @@
         <v>49</v>
       </c>
       <c r="C92" s="35" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D92" s="29" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E92" s="37" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F92" s="31"/>
       <c r="G92" s="31"/>
@@ -8416,13 +8420,13 @@
         <v>49</v>
       </c>
       <c r="C93" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D93" s="29" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E93" s="37" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F93" s="31"/>
       <c r="G93" s="31"/>
@@ -8457,13 +8461,13 @@
         <v>49</v>
       </c>
       <c r="C94" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D94" s="29" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E94" s="37" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F94" s="31"/>
       <c r="G94" s="31"/>
@@ -8498,13 +8502,13 @@
         <v>49</v>
       </c>
       <c r="C95" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D95" s="29" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E95" s="37" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F95" s="31"/>
       <c r="G95" s="31"/>
@@ -8539,13 +8543,13 @@
         <v>49</v>
       </c>
       <c r="C96" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D96" s="29" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E96" s="37" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F96" s="31"/>
       <c r="G96" s="31"/>
@@ -8580,13 +8584,13 @@
         <v>49</v>
       </c>
       <c r="C97" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D97" s="29" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E97" s="37" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F97" s="31"/>
       <c r="G97" s="31"/>
@@ -8621,13 +8625,13 @@
         <v>49</v>
       </c>
       <c r="C98" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D98" s="29" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E98" s="37" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F98" s="31"/>
       <c r="G98" s="31"/>
@@ -8662,13 +8666,13 @@
         <v>49</v>
       </c>
       <c r="C99" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D99" s="29" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E99" s="37" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F99" s="31"/>
       <c r="G99" s="31"/>
@@ -8703,13 +8707,13 @@
         <v>49</v>
       </c>
       <c r="C100" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D100" s="29" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E100" s="37" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F100" s="31"/>
       <c r="G100" s="31"/>
@@ -8744,13 +8748,13 @@
         <v>49</v>
       </c>
       <c r="C101" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D101" s="29" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E101" s="37" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F101" s="31"/>
       <c r="G101" s="31"/>
@@ -8785,13 +8789,13 @@
         <v>49</v>
       </c>
       <c r="C102" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D102" s="29" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E102" s="37" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F102" s="31"/>
       <c r="G102" s="31"/>
@@ -8826,13 +8830,13 @@
         <v>49</v>
       </c>
       <c r="C103" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D103" s="29" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E103" s="37" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F103" s="31"/>
       <c r="G103" s="31"/>
@@ -8867,13 +8871,13 @@
         <v>49</v>
       </c>
       <c r="C104" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D104" s="29" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E104" s="37" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F104" s="31"/>
       <c r="G104" s="31"/>
@@ -8908,13 +8912,13 @@
         <v>49</v>
       </c>
       <c r="C105" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D105" s="29" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E105" s="37" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F105" s="31"/>
       <c r="G105" s="31"/>
@@ -8949,13 +8953,13 @@
         <v>49</v>
       </c>
       <c r="C106" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D106" s="29" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E106" s="37" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F106" s="31"/>
       <c r="G106" s="31"/>
@@ -8990,13 +8994,13 @@
         <v>49</v>
       </c>
       <c r="C107" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D107" s="29" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E107" s="37" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F107" s="31"/>
       <c r="G107" s="31"/>
@@ -9031,13 +9035,13 @@
         <v>49</v>
       </c>
       <c r="C108" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D108" s="29" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E108" s="37" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F108" s="31"/>
       <c r="G108" s="31"/>
@@ -9072,13 +9076,13 @@
         <v>49</v>
       </c>
       <c r="C109" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D109" s="29" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E109" s="37" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F109" s="31"/>
       <c r="G109" s="31"/>
@@ -9113,13 +9117,13 @@
         <v>49</v>
       </c>
       <c r="C110" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D110" s="29" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E110" s="37" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F110" s="31"/>
       <c r="G110" s="31"/>
@@ -9154,13 +9158,13 @@
         <v>49</v>
       </c>
       <c r="C111" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D111" s="29" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E111" s="37" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F111" s="31"/>
       <c r="G111" s="31"/>
@@ -9195,13 +9199,13 @@
         <v>49</v>
       </c>
       <c r="C112" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D112" s="29" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E112" s="37" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F112" s="31"/>
       <c r="G112" s="31"/>
@@ -9236,13 +9240,13 @@
         <v>49</v>
       </c>
       <c r="C113" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D113" s="29" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E113" s="37" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F113" s="31"/>
       <c r="G113" s="31"/>
@@ -9277,13 +9281,13 @@
         <v>49</v>
       </c>
       <c r="C114" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D114" s="29" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E114" s="37" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F114" s="31"/>
       <c r="G114" s="31"/>
@@ -9318,13 +9322,13 @@
         <v>49</v>
       </c>
       <c r="C115" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D115" s="29" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E115" s="37" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F115" s="31"/>
       <c r="G115" s="31"/>
@@ -9362,36 +9366,36 @@
         <v>65</v>
       </c>
       <c r="D116" s="29" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E116" s="37" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F116" s="31" t="s">
         <v>67</v>
       </c>
       <c r="G116" s="31" t="s">
-        <v>68</v>
+        <v>264</v>
       </c>
       <c r="H116" s="31" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="I116" s="36" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="J116" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K116" s="32"/>
       <c r="L116" s="32"/>
       <c r="M116" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N116" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O116" s="32" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="P116" s="32" t="s">
         <v>53</v>
@@ -9400,10 +9404,10 @@
         <v>53</v>
       </c>
       <c r="R116" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="S116" s="32" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="T116" s="32"/>
       <c r="U116" s="33"/>
@@ -9423,36 +9427,36 @@
         <v>65</v>
       </c>
       <c r="D117" s="29" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E117" s="37" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F117" s="31" t="s">
         <v>67</v>
       </c>
       <c r="G117" s="31" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="H117" s="31" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I117" s="36" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J117" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K117" s="32"/>
       <c r="L117" s="32"/>
       <c r="M117" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N117" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O117" s="32" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="P117" s="32" t="s">
         <v>53</v>
@@ -9461,10 +9465,10 @@
         <v>53</v>
       </c>
       <c r="R117" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="S117" s="32" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="T117" s="32"/>
       <c r="U117" s="33"/>
@@ -9484,36 +9488,36 @@
         <v>65</v>
       </c>
       <c r="D118" s="29" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E118" s="37" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F118" s="31" t="s">
         <v>67</v>
       </c>
       <c r="G118" s="31" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="H118" s="31" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I118" s="36" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="J118" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K118" s="32"/>
       <c r="L118" s="32"/>
       <c r="M118" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N118" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O118" s="32" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="P118" s="32" t="s">
         <v>53</v>
@@ -9522,10 +9526,10 @@
         <v>53</v>
       </c>
       <c r="R118" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="S118" s="32" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="T118" s="32"/>
       <c r="U118" s="33"/>
@@ -9545,36 +9549,36 @@
         <v>65</v>
       </c>
       <c r="D119" s="29" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E119" s="37" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F119" s="31" t="s">
         <v>67</v>
       </c>
       <c r="G119" s="31" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="H119" s="31" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I119" s="36" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J119" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K119" s="32"/>
       <c r="L119" s="32"/>
       <c r="M119" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N119" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O119" s="32" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="P119" s="32" t="s">
         <v>53</v>
@@ -9583,10 +9587,10 @@
         <v>53</v>
       </c>
       <c r="R119" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="S119" s="32" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="T119" s="32"/>
       <c r="U119" s="33"/>
@@ -9606,36 +9610,36 @@
         <v>65</v>
       </c>
       <c r="D120" s="29" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E120" s="37" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F120" s="31" t="s">
         <v>67</v>
       </c>
       <c r="G120" s="31" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H120" s="31" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I120" s="36" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="J120" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K120" s="32"/>
       <c r="L120" s="32"/>
       <c r="M120" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N120" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O120" s="32" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="P120" s="32" t="s">
         <v>53</v>
@@ -9644,10 +9648,10 @@
         <v>53</v>
       </c>
       <c r="R120" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="S120" s="32" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="T120" s="32"/>
       <c r="U120" s="33"/>
@@ -9667,36 +9671,36 @@
         <v>65</v>
       </c>
       <c r="D121" s="29" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E121" s="37" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F121" s="31" t="s">
         <v>67</v>
       </c>
       <c r="G121" s="31" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H121" s="31" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I121" s="36" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J121" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K121" s="32"/>
       <c r="L121" s="32"/>
       <c r="M121" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N121" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O121" s="32" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="P121" s="32" t="s">
         <v>53</v>
@@ -9705,10 +9709,10 @@
         <v>53</v>
       </c>
       <c r="R121" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="S121" s="32" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="T121" s="32"/>
       <c r="U121" s="33"/>
@@ -9728,36 +9732,36 @@
         <v>65</v>
       </c>
       <c r="D122" s="29" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E122" s="37" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F122" s="31" t="s">
         <v>67</v>
       </c>
       <c r="G122" s="31" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H122" s="31" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="I122" s="36" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="J122" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K122" s="32"/>
       <c r="L122" s="32"/>
       <c r="M122" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N122" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O122" s="32" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="P122" s="32" t="s">
         <v>53</v>
@@ -9766,10 +9770,10 @@
         <v>53</v>
       </c>
       <c r="R122" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="S122" s="32" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="T122" s="32"/>
       <c r="U122" s="33"/>
@@ -9789,36 +9793,36 @@
         <v>65</v>
       </c>
       <c r="D123" s="29" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E123" s="37" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F123" s="31" t="s">
         <v>67</v>
       </c>
       <c r="G123" s="31" t="s">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="H123" s="31" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="I123" s="36" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="J123" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K123" s="32"/>
       <c r="L123" s="32"/>
       <c r="M123" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N123" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O123" s="32" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="P123" s="32" t="s">
         <v>53</v>
@@ -9827,10 +9831,10 @@
         <v>53</v>
       </c>
       <c r="R123" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="S123" s="32" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="T123" s="32"/>
       <c r="U123" s="33"/>
@@ -9850,36 +9854,36 @@
         <v>65</v>
       </c>
       <c r="D124" s="29" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E124" s="37" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F124" s="31" t="s">
         <v>67</v>
       </c>
       <c r="G124" s="31" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="H124" s="31" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I124" s="36" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J124" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K124" s="32"/>
       <c r="L124" s="32"/>
       <c r="M124" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N124" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O124" s="32" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="P124" s="32" t="s">
         <v>53</v>
@@ -9888,10 +9892,10 @@
         <v>53</v>
       </c>
       <c r="R124" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="S124" s="32" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="T124" s="32"/>
       <c r="U124" s="33"/>
@@ -9911,36 +9915,36 @@
         <v>65</v>
       </c>
       <c r="D125" s="29" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E125" s="37" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F125" s="31" t="s">
         <v>67</v>
       </c>
       <c r="G125" s="31" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="H125" s="31" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="I125" s="36" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J125" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K125" s="32"/>
       <c r="L125" s="32"/>
       <c r="M125" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N125" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O125" s="32" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="P125" s="32" t="s">
         <v>53</v>
@@ -9949,10 +9953,10 @@
         <v>53</v>
       </c>
       <c r="R125" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="S125" s="32" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="T125" s="32"/>
       <c r="U125" s="33"/>
@@ -9972,36 +9976,36 @@
         <v>65</v>
       </c>
       <c r="D126" s="29" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E126" s="37" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F126" s="31" t="s">
         <v>67</v>
       </c>
       <c r="G126" s="31" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="H126" s="31" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="I126" s="36" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J126" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K126" s="32"/>
       <c r="L126" s="32"/>
       <c r="M126" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N126" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O126" s="32" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="P126" s="32" t="s">
         <v>53</v>
@@ -10010,10 +10014,10 @@
         <v>53</v>
       </c>
       <c r="R126" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="S126" s="32" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="T126" s="32"/>
       <c r="U126" s="33"/>
@@ -10033,36 +10037,36 @@
         <v>65</v>
       </c>
       <c r="D127" s="29" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E127" s="37" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F127" s="31" t="s">
         <v>67</v>
       </c>
       <c r="G127" s="31" t="s">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="H127" s="31" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="I127" s="36" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="J127" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K127" s="32"/>
       <c r="L127" s="32"/>
       <c r="M127" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N127" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O127" s="32" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="P127" s="32" t="s">
         <v>53</v>
@@ -10071,10 +10075,10 @@
         <v>53</v>
       </c>
       <c r="R127" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="S127" s="32" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="T127" s="32"/>
       <c r="U127" s="33"/>
@@ -10094,36 +10098,36 @@
         <v>65</v>
       </c>
       <c r="D128" s="29" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E128" s="37" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F128" s="31" t="s">
         <v>67</v>
       </c>
       <c r="G128" s="31" t="s">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="H128" s="31" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="I128" s="36" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="J128" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K128" s="32"/>
       <c r="L128" s="32"/>
       <c r="M128" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N128" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O128" s="32" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="P128" s="32" t="s">
         <v>53</v>
@@ -10132,10 +10136,10 @@
         <v>53</v>
       </c>
       <c r="R128" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="S128" s="32" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="T128" s="32"/>
       <c r="U128" s="33"/>
@@ -10155,36 +10159,36 @@
         <v>65</v>
       </c>
       <c r="D129" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E129" s="37" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F129" s="31" t="s">
         <v>67</v>
       </c>
       <c r="G129" s="31" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="H129" s="31" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="I129" s="36" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="J129" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K129" s="32"/>
       <c r="L129" s="32"/>
       <c r="M129" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N129" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O129" s="32" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="P129" s="32" t="s">
         <v>53</v>
@@ -10193,10 +10197,10 @@
         <v>53</v>
       </c>
       <c r="R129" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="S129" s="32" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="T129" s="32"/>
       <c r="U129" s="33"/>
@@ -10216,36 +10220,36 @@
         <v>65</v>
       </c>
       <c r="D130" s="29" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E130" s="37" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F130" s="31" t="s">
         <v>67</v>
       </c>
       <c r="G130" s="31" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="H130" s="31" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="I130" s="36" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="J130" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K130" s="32"/>
       <c r="L130" s="32"/>
       <c r="M130" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N130" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O130" s="32" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="P130" s="32" t="s">
         <v>53</v>
@@ -10254,10 +10258,10 @@
         <v>53</v>
       </c>
       <c r="R130" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="S130" s="32" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="T130" s="32"/>
       <c r="U130" s="33"/>
@@ -10277,10 +10281,10 @@
         <v>61</v>
       </c>
       <c r="D131" s="29" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E131" s="37" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F131" s="31"/>
       <c r="G131" s="31"/>
@@ -10318,10 +10322,10 @@
         <v>61</v>
       </c>
       <c r="D132" s="29" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E132" s="37" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F132" s="31"/>
       <c r="G132" s="31"/>
@@ -10359,10 +10363,10 @@
         <v>61</v>
       </c>
       <c r="D133" s="29" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E133" s="37" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F133" s="31"/>
       <c r="G133" s="31"/>
@@ -10400,10 +10404,10 @@
         <v>61</v>
       </c>
       <c r="D134" s="29" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E134" s="37" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F134" s="31"/>
       <c r="G134" s="31"/>
@@ -10441,10 +10445,10 @@
         <v>61</v>
       </c>
       <c r="D135" s="29" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E135" s="37" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F135" s="31"/>
       <c r="G135" s="31"/>
@@ -10482,10 +10486,10 @@
         <v>61</v>
       </c>
       <c r="D136" s="29" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E136" s="37" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F136" s="31"/>
       <c r="G136" s="31"/>
@@ -10523,10 +10527,10 @@
         <v>61</v>
       </c>
       <c r="D137" s="29" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E137" s="37" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="F137" s="31"/>
       <c r="G137" s="31"/>
@@ -10564,10 +10568,10 @@
         <v>61</v>
       </c>
       <c r="D138" s="29" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E138" s="37" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F138" s="31"/>
       <c r="G138" s="31"/>
@@ -10605,10 +10609,10 @@
         <v>61</v>
       </c>
       <c r="D139" s="29" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E139" s="37" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F139" s="31"/>
       <c r="G139" s="31"/>
@@ -10646,10 +10650,10 @@
         <v>61</v>
       </c>
       <c r="D140" s="29" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E140" s="37" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F140" s="31"/>
       <c r="G140" s="31"/>
@@ -10687,10 +10691,10 @@
         <v>61</v>
       </c>
       <c r="D141" s="29" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E141" s="37" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F141" s="31"/>
       <c r="G141" s="31"/>
@@ -10728,10 +10732,10 @@
         <v>61</v>
       </c>
       <c r="D142" s="29" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E142" s="37" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F142" s="31"/>
       <c r="G142" s="31"/>
@@ -10769,10 +10773,10 @@
         <v>61</v>
       </c>
       <c r="D143" s="29" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E143" s="37" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F143" s="31"/>
       <c r="G143" s="31"/>
@@ -10810,10 +10814,10 @@
         <v>61</v>
       </c>
       <c r="D144" s="29" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E144" s="37" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F144" s="31"/>
       <c r="G144" s="31"/>
@@ -10851,10 +10855,10 @@
         <v>61</v>
       </c>
       <c r="D145" s="29" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E145" s="37" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F145" s="31"/>
       <c r="G145" s="31"/>
@@ -10892,10 +10896,10 @@
         <v>50</v>
       </c>
       <c r="D146" s="29" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E146" s="37" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F146" s="31"/>
       <c r="G146" s="31"/>
@@ -10933,10 +10937,10 @@
         <v>50</v>
       </c>
       <c r="D147" s="29" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E147" s="37" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F147" s="31"/>
       <c r="G147" s="31"/>
@@ -10971,13 +10975,13 @@
         <v>49</v>
       </c>
       <c r="C148" s="35" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D148" s="29" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E148" s="37" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F148" s="31"/>
       <c r="G148" s="31"/>
@@ -11012,13 +11016,13 @@
         <v>49</v>
       </c>
       <c r="C149" s="35" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D149" s="29" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E149" s="37" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F149" s="31"/>
       <c r="G149" s="31"/>
@@ -11053,13 +11057,13 @@
         <v>49</v>
       </c>
       <c r="C150" s="35" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D150" s="29" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E150" s="37" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F150" s="31"/>
       <c r="G150" s="31"/>
@@ -11094,10 +11098,10 @@
         <v>49</v>
       </c>
       <c r="C151" s="35" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D151" s="29" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E151" s="37" t="s">
         <v>57</v>
@@ -11135,13 +11139,13 @@
         <v>49</v>
       </c>
       <c r="C152" s="35" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D152" s="29" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E152" s="37" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F152" s="31"/>
       <c r="G152" s="31"/>
@@ -11176,13 +11180,13 @@
         <v>49</v>
       </c>
       <c r="C153" s="35" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D153" s="29" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E153" s="37" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F153" s="31"/>
       <c r="G153" s="31"/>
@@ -11204,7 +11208,7 @@
       <c r="S153" s="32"/>
       <c r="T153" s="32"/>
       <c r="U153" s="33" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="V153" s="34"/>
       <c r="W153" s="32" t="s">
@@ -11219,13 +11223,13 @@
         <v>49</v>
       </c>
       <c r="C154" s="35" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D154" s="29" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E154" s="37" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F154" s="31"/>
       <c r="G154" s="31"/>
@@ -11260,13 +11264,13 @@
         <v>49</v>
       </c>
       <c r="C155" s="35" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D155" s="29" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E155" s="37" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F155" s="31"/>
       <c r="G155" s="31"/>
@@ -11301,13 +11305,13 @@
         <v>49</v>
       </c>
       <c r="C156" s="35" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D156" s="29" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E156" s="37" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F156" s="31"/>
       <c r="G156" s="31"/>
@@ -11342,13 +11346,13 @@
         <v>49</v>
       </c>
       <c r="C157" s="35" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D157" s="29" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E157" s="37" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F157" s="31"/>
       <c r="G157" s="31"/>
@@ -11383,13 +11387,13 @@
         <v>49</v>
       </c>
       <c r="C158" s="35" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D158" s="29" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E158" s="37" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F158" s="31"/>
       <c r="G158" s="31"/>
@@ -11424,13 +11428,13 @@
         <v>49</v>
       </c>
       <c r="C159" s="35" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D159" s="29" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E159" s="37" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F159" s="31"/>
       <c r="G159" s="31"/>
@@ -11465,13 +11469,13 @@
         <v>49</v>
       </c>
       <c r="C160" s="35" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D160" s="29" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E160" s="37" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F160" s="31"/>
       <c r="G160" s="31"/>
@@ -11506,13 +11510,13 @@
         <v>49</v>
       </c>
       <c r="C161" s="35" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D161" s="29" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E161" s="37" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F161" s="31"/>
       <c r="G161" s="31"/>
@@ -11547,13 +11551,13 @@
         <v>49</v>
       </c>
       <c r="C162" s="35" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D162" s="29" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E162" s="37" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F162" s="31"/>
       <c r="G162" s="31"/>
@@ -11588,13 +11592,13 @@
         <v>49</v>
       </c>
       <c r="C163" s="35" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D163" s="29" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E163" s="37" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F163" s="31"/>
       <c r="G163" s="31"/>
@@ -11632,10 +11636,10 @@
         <v>65</v>
       </c>
       <c r="D164" s="29" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E164" s="37" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="F164" s="31" t="s">
         <v>67</v>
@@ -11644,13 +11648,13 @@
         <v>68</v>
       </c>
       <c r="H164" s="31" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="I164" s="36" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="J164" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K164" s="32"/>
       <c r="L164" s="32"/>
@@ -11679,10 +11683,10 @@
         <v>65</v>
       </c>
       <c r="D165" s="29" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E165" s="37" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F165" s="31" t="s">
         <v>67</v>
@@ -11691,13 +11695,13 @@
         <v>68</v>
       </c>
       <c r="H165" s="31" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="I165" s="36" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="J165" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K165" s="32"/>
       <c r="L165" s="32"/>
@@ -11726,10 +11730,10 @@
         <v>59</v>
       </c>
       <c r="D166" s="29" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E166" s="37" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="F166" s="31"/>
       <c r="G166" s="31"/>
@@ -11767,10 +11771,10 @@
         <v>59</v>
       </c>
       <c r="D167" s="29" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E167" s="37" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="F167" s="31"/>
       <c r="G167" s="31"/>
@@ -11808,10 +11812,10 @@
         <v>50</v>
       </c>
       <c r="D168" s="29" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E168" s="37" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F168" s="31"/>
       <c r="G168" s="31"/>
@@ -11846,13 +11850,13 @@
         <v>49</v>
       </c>
       <c r="C169" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D169" s="29" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E169" s="37" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F169" s="31"/>
       <c r="G169" s="31"/>
@@ -11887,13 +11891,13 @@
         <v>49</v>
       </c>
       <c r="C170" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D170" s="29" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E170" s="37" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="F170" s="31"/>
       <c r="G170" s="31"/>
@@ -11928,13 +11932,13 @@
         <v>49</v>
       </c>
       <c r="C171" s="35" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D171" s="29" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E171" s="37" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F171" s="31"/>
       <c r="G171" s="31"/>
@@ -11969,13 +11973,13 @@
         <v>49</v>
       </c>
       <c r="C172" s="35" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D172" s="29" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E172" s="37" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="F172" s="31"/>
       <c r="G172" s="31"/>
@@ -12010,13 +12014,13 @@
         <v>49</v>
       </c>
       <c r="C173" s="35" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D173" s="29" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E173" s="37" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="F173" s="31"/>
       <c r="G173" s="31"/>
@@ -12051,13 +12055,13 @@
         <v>49</v>
       </c>
       <c r="C174" s="35" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D174" s="29" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E174" s="37" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="F174" s="31"/>
       <c r="G174" s="31"/>
@@ -12092,13 +12096,13 @@
         <v>49</v>
       </c>
       <c r="C175" s="35" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D175" s="29" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E175" s="37" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="F175" s="31"/>
       <c r="G175" s="31"/>
@@ -12136,36 +12140,36 @@
         <v>65</v>
       </c>
       <c r="D176" s="29" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E176" s="37" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="F176" s="29" t="s">
         <v>67</v>
       </c>
       <c r="G176" s="29" t="s">
-        <v>422</v>
+        <v>326</v>
       </c>
       <c r="H176" s="29" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="I176" s="29" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="J176" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K176" s="32"/>
       <c r="L176" s="29"/>
       <c r="M176" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N176" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O176" s="29" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="P176" s="32" t="s">
         <v>53</v>
@@ -12174,10 +12178,10 @@
         <v>53</v>
       </c>
       <c r="R176" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="S176" s="29" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="T176" s="32"/>
       <c r="U176" s="29"/>
@@ -12197,10 +12201,10 @@
         <v>63</v>
       </c>
       <c r="D177" s="29" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E177" s="37" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F177" s="29"/>
       <c r="G177" s="29"/>
@@ -12235,13 +12239,13 @@
         <v>49</v>
       </c>
       <c r="C178" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D178" s="29" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E178" s="37" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F178" s="29"/>
       <c r="G178" s="29"/>
@@ -12276,13 +12280,13 @@
         <v>49</v>
       </c>
       <c r="C179" s="35" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D179" s="29" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E179" s="37" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F179" s="29"/>
       <c r="G179" s="29"/>
@@ -12317,13 +12321,13 @@
         <v>49</v>
       </c>
       <c r="C180" s="35" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D180" s="29" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E180" s="37" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F180" s="29"/>
       <c r="G180" s="29"/>
@@ -12361,10 +12365,10 @@
         <v>50</v>
       </c>
       <c r="D181" s="29" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E181" s="37" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F181" s="29"/>
       <c r="G181" s="29"/>
@@ -12402,10 +12406,10 @@
         <v>59</v>
       </c>
       <c r="D182" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E182" s="37" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F182" s="29"/>
       <c r="G182" s="29"/>
@@ -12443,34 +12447,34 @@
         <v>65</v>
       </c>
       <c r="D183" s="29" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E183" s="37" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F183" s="29" t="s">
         <v>67</v>
       </c>
       <c r="G183" s="29" t="s">
-        <v>422</v>
+        <v>326</v>
       </c>
       <c r="H183" s="29" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="I183" s="29"/>
       <c r="J183" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K183" s="32"/>
       <c r="L183" s="29"/>
       <c r="M183" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N183" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O183" s="29" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="P183" s="32" t="s">
         <v>53</v>
@@ -12479,10 +12483,10 @@
         <v>53</v>
       </c>
       <c r="R183" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="S183" s="29" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="T183" s="32"/>
       <c r="U183" s="29"/>
@@ -12502,10 +12506,10 @@
         <v>61</v>
       </c>
       <c r="D184" s="29" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E184" s="37" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F184" s="29"/>
       <c r="G184" s="29"/>
@@ -12540,13 +12544,13 @@
         <v>49</v>
       </c>
       <c r="C185" s="35" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D185" s="29" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E185" s="37" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F185" s="29"/>
       <c r="G185" s="29"/>
@@ -12584,10 +12588,10 @@
         <v>63</v>
       </c>
       <c r="D186" s="29" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E186" s="37" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F186" s="31"/>
       <c r="G186" s="31"/>
@@ -12625,10 +12629,10 @@
         <v>63</v>
       </c>
       <c r="D187" s="29" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E187" s="37" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F187" s="31"/>
       <c r="G187" s="31"/>
@@ -12666,10 +12670,10 @@
         <v>50</v>
       </c>
       <c r="D188" s="35" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E188" s="37" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F188" s="31"/>
       <c r="G188" s="31"/>
@@ -12707,10 +12711,10 @@
         <v>63</v>
       </c>
       <c r="D189" s="29" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E189" s="37" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F189" s="31"/>
       <c r="G189" s="31"/>
@@ -12748,36 +12752,36 @@
         <v>65</v>
       </c>
       <c r="D190" s="29" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E190" s="37" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F190" s="31" t="s">
         <v>67</v>
       </c>
       <c r="G190" s="31" t="s">
-        <v>422</v>
+        <v>455</v>
       </c>
       <c r="H190" s="31" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="I190" s="36" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="J190" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K190" s="32"/>
       <c r="L190" s="32"/>
       <c r="M190" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N190" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O190" s="32" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="P190" s="32" t="s">
         <v>53</v>
@@ -12786,10 +12790,10 @@
         <v>53</v>
       </c>
       <c r="R190" s="32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="S190" s="32" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="T190" s="32"/>
       <c r="U190" s="33"/>
@@ -12809,10 +12813,10 @@
         <v>61</v>
       </c>
       <c r="D191" s="29" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E191" s="37" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="F191" s="31"/>
       <c r="G191" s="31"/>
@@ -12850,10 +12854,10 @@
         <v>61</v>
       </c>
       <c r="D192" s="29" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E192" s="37" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="F192" s="31"/>
       <c r="G192" s="31"/>
@@ -12891,10 +12895,10 @@
         <v>61</v>
       </c>
       <c r="D193" s="29" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E193" s="40" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F193" s="31"/>
       <c r="G193" s="31"/>
@@ -12929,13 +12933,13 @@
         <v>49</v>
       </c>
       <c r="C194" s="35" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D194" s="29" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E194" s="40" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="F194" s="31"/>
       <c r="G194" s="31"/>
@@ -12970,13 +12974,13 @@
         <v>49</v>
       </c>
       <c r="C195" s="35" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D195" s="29" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E195" s="40" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F195" s="31"/>
       <c r="G195" s="31"/>
@@ -13011,13 +13015,13 @@
         <v>49</v>
       </c>
       <c r="C196" s="35" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D196" s="29" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E196" s="40" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F196" s="31"/>
       <c r="G196" s="31"/>
@@ -13052,13 +13056,13 @@
         <v>49</v>
       </c>
       <c r="C197" s="35" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D197" s="29" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E197" s="40" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="F197" s="31"/>
       <c r="G197" s="31"/>
@@ -13093,13 +13097,13 @@
         <v>49</v>
       </c>
       <c r="C198" s="35" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D198" s="29" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E198" s="40" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="F198" s="31"/>
       <c r="G198" s="31"/>
@@ -13134,13 +13138,13 @@
         <v>49</v>
       </c>
       <c r="C199" s="35" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D199" s="29" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E199" s="40" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="F199" s="31"/>
       <c r="G199" s="31"/>
@@ -13175,13 +13179,13 @@
         <v>49</v>
       </c>
       <c r="C200" s="35" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D200" s="29" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E200" s="40" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F200" s="31"/>
       <c r="G200" s="31"/>
@@ -13216,13 +13220,13 @@
         <v>49</v>
       </c>
       <c r="C201" s="35" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D201" s="29" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="E201" s="40" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F201" s="31"/>
       <c r="G201" s="31"/>
@@ -13257,13 +13261,13 @@
         <v>49</v>
       </c>
       <c r="C202" s="35" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D202" s="29" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E202" s="40" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="F202" s="31"/>
       <c r="G202" s="31"/>
@@ -13298,13 +13302,13 @@
         <v>49</v>
       </c>
       <c r="C203" s="35" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D203" s="29" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E203" s="40" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="F203" s="31"/>
       <c r="G203" s="31"/>
@@ -13339,13 +13343,13 @@
         <v>49</v>
       </c>
       <c r="C204" s="35" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D204" s="29" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E204" s="37" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F204" s="31"/>
       <c r="G204" s="31"/>
@@ -13380,13 +13384,13 @@
         <v>49</v>
       </c>
       <c r="C205" s="35" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D205" s="29" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E205" s="37" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F205" s="31"/>
       <c r="G205" s="31"/>
@@ -13408,7 +13412,7 @@
       <c r="S205" s="32"/>
       <c r="T205" s="32"/>
       <c r="U205" s="33" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="V205" s="34"/>
       <c r="W205" s="32" t="s">
@@ -13423,13 +13427,13 @@
         <v>49</v>
       </c>
       <c r="C206" s="35" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D206" s="29" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E206" s="40" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="F206" s="31"/>
       <c r="G206" s="31"/>
@@ -13464,13 +13468,13 @@
         <v>49</v>
       </c>
       <c r="C207" s="35" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D207" s="29" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="E207" s="40" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="F207" s="31"/>
       <c r="G207" s="31"/>
@@ -13505,13 +13509,13 @@
         <v>49</v>
       </c>
       <c r="C208" s="35" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D208" s="29" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="E208" s="40" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="F208" s="31"/>
       <c r="G208" s="31"/>
@@ -13546,13 +13550,13 @@
         <v>49</v>
       </c>
       <c r="C209" s="35" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D209" s="29" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E209" s="40" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F209" s="31"/>
       <c r="G209" s="31"/>
@@ -13587,13 +13591,13 @@
         <v>49</v>
       </c>
       <c r="C210" s="35" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D210" s="29" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E210" s="40" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F210" s="31"/>
       <c r="G210" s="31"/>
@@ -13628,13 +13632,13 @@
         <v>49</v>
       </c>
       <c r="C211" s="35" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D211" s="29" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="E211" s="40" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="F211" s="31"/>
       <c r="G211" s="31"/>
@@ -13669,13 +13673,13 @@
         <v>49</v>
       </c>
       <c r="C212" s="35" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D212" s="29" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="E212" s="40" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="F212" s="31"/>
       <c r="G212" s="31"/>
@@ -13710,13 +13714,13 @@
         <v>49</v>
       </c>
       <c r="C213" s="35" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D213" s="29" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="E213" s="40" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="F213" s="31"/>
       <c r="G213" s="31"/>
@@ -13751,13 +13755,13 @@
         <v>49</v>
       </c>
       <c r="C214" s="35" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D214" s="29" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="E214" s="40" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="F214" s="31"/>
       <c r="G214" s="31"/>
@@ -13792,13 +13796,13 @@
         <v>49</v>
       </c>
       <c r="C215" s="35" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D215" s="29" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="E215" s="40" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="F215" s="31"/>
       <c r="G215" s="31"/>
@@ -13833,13 +13837,13 @@
         <v>49</v>
       </c>
       <c r="C216" s="35" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D216" s="29" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="E216" s="40" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="F216" s="31"/>
       <c r="G216" s="31"/>
@@ -13874,13 +13878,13 @@
         <v>49</v>
       </c>
       <c r="C217" s="35" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D217" s="29" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="E217" s="40" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="F217" s="31"/>
       <c r="G217" s="31"/>
@@ -13915,13 +13919,13 @@
         <v>49</v>
       </c>
       <c r="C218" s="35" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D218" s="29" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E218" s="40" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F218" s="31"/>
       <c r="G218" s="31"/>
@@ -13956,13 +13960,13 @@
         <v>49</v>
       </c>
       <c r="C219" s="35" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D219" s="29" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E219" s="37" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F219" s="31"/>
       <c r="G219" s="31"/>
@@ -13997,13 +14001,13 @@
         <v>49</v>
       </c>
       <c r="C220" s="35" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D220" s="29" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E220" s="37" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F220" s="31"/>
       <c r="G220" s="31"/>
@@ -14025,7 +14029,7 @@
       <c r="S220" s="32"/>
       <c r="T220" s="32"/>
       <c r="U220" s="33" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="V220" s="34"/>
       <c r="W220" s="32" t="s">
@@ -14040,13 +14044,13 @@
         <v>49</v>
       </c>
       <c r="C221" s="35" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D221" s="29" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E221" s="40" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="F221" s="31"/>
       <c r="G221" s="31"/>
@@ -14081,13 +14085,13 @@
         <v>49</v>
       </c>
       <c r="C222" s="35" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D222" s="29" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="E222" s="40" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="F222" s="31"/>
       <c r="G222" s="31"/>
@@ -14122,13 +14126,13 @@
         <v>49</v>
       </c>
       <c r="C223" s="35" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D223" s="29" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="E223" s="40" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="F223" s="31"/>
       <c r="G223" s="31"/>
@@ -14163,13 +14167,13 @@
         <v>49</v>
       </c>
       <c r="C224" s="35" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D224" s="29" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E224" s="40" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="F224" s="31"/>
       <c r="G224" s="31"/>
@@ -14204,13 +14208,13 @@
         <v>49</v>
       </c>
       <c r="C225" s="35" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D225" s="29" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E225" s="40" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="F225" s="31"/>
       <c r="G225" s="31"/>
@@ -14245,13 +14249,13 @@
         <v>49</v>
       </c>
       <c r="C226" s="35" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D226" s="29" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="E226" s="40" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="F226" s="31"/>
       <c r="G226" s="31"/>
@@ -14286,13 +14290,13 @@
         <v>49</v>
       </c>
       <c r="C227" s="35" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D227" s="29" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="E227" s="40" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="F227" s="31"/>
       <c r="G227" s="31"/>
@@ -14327,13 +14331,13 @@
         <v>49</v>
       </c>
       <c r="C228" s="35" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D228" s="29" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E228" s="40" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="F228" s="31"/>
       <c r="G228" s="31"/>
@@ -14368,13 +14372,13 @@
         <v>49</v>
       </c>
       <c r="C229" s="35" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D229" s="29" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E229" s="40" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="F229" s="31"/>
       <c r="G229" s="31"/>
@@ -14409,13 +14413,13 @@
         <v>49</v>
       </c>
       <c r="C230" s="35" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D230" s="29" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="E230" s="40" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="F230" s="31"/>
       <c r="G230" s="31"/>
@@ -14450,13 +14454,13 @@
         <v>49</v>
       </c>
       <c r="C231" s="35" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D231" s="29" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="E231" s="40" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="F231" s="31"/>
       <c r="G231" s="31"/>
@@ -14491,13 +14495,13 @@
         <v>49</v>
       </c>
       <c r="C232" s="35" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D232" s="29" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="E232" s="40" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="F232" s="31"/>
       <c r="G232" s="31"/>
@@ -14532,13 +14536,13 @@
         <v>49</v>
       </c>
       <c r="C233" s="35" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D233" s="29" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="E233" s="40" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="F233" s="31"/>
       <c r="G233" s="31"/>
@@ -14573,13 +14577,13 @@
         <v>49</v>
       </c>
       <c r="C234" s="35" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D234" s="29" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="E234" s="37" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F234" s="31"/>
       <c r="G234" s="31"/>
@@ -14614,13 +14618,13 @@
         <v>49</v>
       </c>
       <c r="C235" s="35" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D235" s="29" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="E235" s="37" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F235" s="31"/>
       <c r="G235" s="31"/>
@@ -14642,7 +14646,7 @@
       <c r="S235" s="32"/>
       <c r="T235" s="32"/>
       <c r="U235" s="33" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="V235" s="34"/>
       <c r="W235" s="32" t="s">
@@ -14657,13 +14661,13 @@
         <v>49</v>
       </c>
       <c r="C236" s="42" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D236" s="41" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="E236" s="40" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="F236" s="43"/>
       <c r="G236" s="43"/>
@@ -14698,13 +14702,13 @@
         <v>49</v>
       </c>
       <c r="C237" s="42" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D237" s="41" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="E237" s="40" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F237" s="43"/>
       <c r="G237" s="43"/>
@@ -14739,13 +14743,13 @@
         <v>49</v>
       </c>
       <c r="C238" s="42" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D238" s="41" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E238" s="40" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="F238" s="43"/>
       <c r="G238" s="43"/>
@@ -14780,13 +14784,13 @@
         <v>49</v>
       </c>
       <c r="C239" s="42" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D239" s="41" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="E239" s="40" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="F239" s="43"/>
       <c r="G239" s="43"/>
@@ -14821,13 +14825,13 @@
         <v>49</v>
       </c>
       <c r="C240" s="42" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D240" s="41" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E240" s="40" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="F240" s="43"/>
       <c r="G240" s="43"/>
@@ -14862,13 +14866,13 @@
         <v>49</v>
       </c>
       <c r="C241" s="42" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D241" s="41" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="E241" s="40" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="F241" s="43"/>
       <c r="G241" s="43"/>
@@ -14903,13 +14907,13 @@
         <v>49</v>
       </c>
       <c r="C242" s="42" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D242" s="41" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="E242" s="40" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="F242" s="43"/>
       <c r="G242" s="43"/>
@@ -14944,13 +14948,13 @@
         <v>49</v>
       </c>
       <c r="C243" s="42" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D243" s="41" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="E243" s="40" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="F243" s="43"/>
       <c r="G243" s="43"/>
@@ -14985,13 +14989,13 @@
         <v>49</v>
       </c>
       <c r="C244" s="42" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D244" s="41" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="E244" s="40" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F244" s="43"/>
       <c r="G244" s="43"/>
@@ -15026,13 +15030,13 @@
         <v>49</v>
       </c>
       <c r="C245" s="42" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D245" s="41" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="E245" s="40" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F245" s="43"/>
       <c r="G245" s="43"/>
@@ -15054,7 +15058,7 @@
       <c r="S245" s="45"/>
       <c r="T245" s="45"/>
       <c r="U245" s="46" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="V245" s="47"/>
       <c r="W245" s="45" t="s">
@@ -15069,13 +15073,13 @@
         <v>49</v>
       </c>
       <c r="C246" s="62" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D246" s="61" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="E246" s="63" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="F246" s="64"/>
       <c r="G246" s="64"/>
@@ -15110,13 +15114,13 @@
         <v>49</v>
       </c>
       <c r="C247" s="62" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D247" s="61" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="E247" s="63" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="F247" s="64"/>
       <c r="G247" s="64"/>
@@ -15151,13 +15155,13 @@
         <v>49</v>
       </c>
       <c r="C248" s="62" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D248" s="61" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="E248" s="63" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="F248" s="64"/>
       <c r="G248" s="64"/>
@@ -15192,13 +15196,13 @@
         <v>49</v>
       </c>
       <c r="C249" s="62" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D249" s="61" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E249" s="63" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="F249" s="64"/>
       <c r="G249" s="64"/>
@@ -15233,13 +15237,13 @@
         <v>49</v>
       </c>
       <c r="C250" s="62" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D250" s="61" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E250" s="63" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="F250" s="64"/>
       <c r="G250" s="64"/>
@@ -15274,13 +15278,13 @@
         <v>49</v>
       </c>
       <c r="C251" s="62" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D251" s="61" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E251" s="63" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="F251" s="64"/>
       <c r="G251" s="64"/>
@@ -15315,13 +15319,13 @@
         <v>49</v>
       </c>
       <c r="C252" s="62" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D252" s="61" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="E252" s="63" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="F252" s="64"/>
       <c r="G252" s="64"/>
@@ -15356,13 +15360,13 @@
         <v>49</v>
       </c>
       <c r="C253" s="62" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D253" s="61" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="E253" s="63" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="F253" s="64"/>
       <c r="G253" s="64"/>
@@ -15397,13 +15401,13 @@
         <v>49</v>
       </c>
       <c r="C254" s="62" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D254" s="61" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="E254" s="63" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="F254" s="64"/>
       <c r="G254" s="64"/>
@@ -15438,13 +15442,13 @@
         <v>49</v>
       </c>
       <c r="C255" s="62" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D255" s="61" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="E255" s="63" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="F255" s="64"/>
       <c r="G255" s="64"/>
@@ -15479,13 +15483,13 @@
         <v>49</v>
       </c>
       <c r="C256" s="62" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D256" s="61" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="E256" s="63" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="F256" s="64"/>
       <c r="G256" s="64"/>
@@ -15520,13 +15524,13 @@
         <v>49</v>
       </c>
       <c r="C257" s="62" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D257" s="61" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="E257" s="63" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="F257" s="64"/>
       <c r="G257" s="64"/>
@@ -15561,13 +15565,13 @@
         <v>49</v>
       </c>
       <c r="C258" s="62" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D258" s="61" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="E258" s="63" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="F258" s="64"/>
       <c r="G258" s="64"/>
@@ -15602,13 +15606,13 @@
         <v>49</v>
       </c>
       <c r="C259" s="62" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D259" s="61" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="E259" s="63" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="F259" s="64"/>
       <c r="G259" s="64"/>
@@ -15643,13 +15647,13 @@
         <v>49</v>
       </c>
       <c r="C260" s="62" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D260" s="61" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="E260" s="63" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="F260" s="64"/>
       <c r="G260" s="64"/>
@@ -15684,13 +15688,13 @@
         <v>49</v>
       </c>
       <c r="C261" s="62" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D261" s="61" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="E261" s="63" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="F261" s="64"/>
       <c r="G261" s="64"/>
@@ -15725,13 +15729,13 @@
         <v>49</v>
       </c>
       <c r="C262" s="62" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D262" s="61" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="E262" s="63" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="F262" s="64"/>
       <c r="G262" s="64"/>
@@ -15766,13 +15770,13 @@
         <v>49</v>
       </c>
       <c r="C263" s="62" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D263" s="61" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="E263" s="63" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="F263" s="64"/>
       <c r="G263" s="64"/>
@@ -15807,13 +15811,13 @@
         <v>49</v>
       </c>
       <c r="C264" s="62" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D264" s="61" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="E264" s="63" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F264" s="64"/>
       <c r="G264" s="64"/>
@@ -15848,13 +15852,13 @@
         <v>49</v>
       </c>
       <c r="C265" s="62" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D265" s="61" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="E265" s="63" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F265" s="64"/>
       <c r="G265" s="64"/>
@@ -15876,7 +15880,7 @@
       <c r="S265" s="66"/>
       <c r="T265" s="66"/>
       <c r="U265" s="67" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="V265" s="68"/>
       <c r="W265" s="66" t="s">
@@ -15891,13 +15895,13 @@
         <v>49</v>
       </c>
       <c r="C266" s="62" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D266" s="61" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="E266" s="63" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="F266" s="64"/>
       <c r="G266" s="64"/>
@@ -15932,13 +15936,13 @@
         <v>49</v>
       </c>
       <c r="C267" s="62" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D267" s="61" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="E267" s="63" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="F267" s="64"/>
       <c r="G267" s="64"/>
@@ -15973,13 +15977,13 @@
         <v>49</v>
       </c>
       <c r="C268" s="62" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D268" s="61" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="E268" s="63" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="F268" s="64"/>
       <c r="G268" s="64"/>
@@ -16014,13 +16018,13 @@
         <v>49</v>
       </c>
       <c r="C269" s="62" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D269" s="61" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="E269" s="63" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="F269" s="64"/>
       <c r="G269" s="64"/>
@@ -16055,13 +16059,13 @@
         <v>49</v>
       </c>
       <c r="C270" s="62" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D270" s="61" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="E270" s="63" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="F270" s="64"/>
       <c r="G270" s="64"/>
@@ -16096,13 +16100,13 @@
         <v>49</v>
       </c>
       <c r="C271" s="62" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D271" s="61" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="E271" s="63" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="F271" s="64"/>
       <c r="G271" s="64"/>
@@ -16137,13 +16141,13 @@
         <v>49</v>
       </c>
       <c r="C272" s="62" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D272" s="61" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="E272" s="63" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="F272" s="64"/>
       <c r="G272" s="64"/>
@@ -16178,13 +16182,13 @@
         <v>49</v>
       </c>
       <c r="C273" s="62" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D273" s="61" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="E273" s="63" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="F273" s="64"/>
       <c r="G273" s="64"/>
@@ -16219,13 +16223,13 @@
         <v>49</v>
       </c>
       <c r="C274" s="62" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D274" s="61" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="E274" s="63" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="F274" s="64"/>
       <c r="G274" s="64"/>
@@ -16260,13 +16264,13 @@
         <v>49</v>
       </c>
       <c r="C275" s="62" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D275" s="61" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="E275" s="63" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="F275" s="64"/>
       <c r="G275" s="64"/>
@@ -16301,13 +16305,13 @@
         <v>49</v>
       </c>
       <c r="C276" s="62" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D276" s="61" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="E276" s="63" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="F276" s="64"/>
       <c r="G276" s="64"/>
@@ -16342,13 +16346,13 @@
         <v>49</v>
       </c>
       <c r="C277" s="62" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D277" s="61" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="E277" s="63" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="F277" s="64"/>
       <c r="G277" s="64"/>
@@ -16383,13 +16387,13 @@
         <v>49</v>
       </c>
       <c r="C278" s="62" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D278" s="61" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="E278" s="63" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="F278" s="64"/>
       <c r="G278" s="64"/>
@@ -16424,13 +16428,13 @@
         <v>49</v>
       </c>
       <c r="C279" s="62" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D279" s="61" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E279" s="63" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="F279" s="64"/>
       <c r="G279" s="64"/>
@@ -16465,13 +16469,13 @@
         <v>49</v>
       </c>
       <c r="C280" s="62" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D280" s="61" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="E280" s="63" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="F280" s="64"/>
       <c r="G280" s="64"/>
@@ -16506,13 +16510,13 @@
         <v>49</v>
       </c>
       <c r="C281" s="62" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D281" s="61" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="E281" s="63" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="F281" s="64"/>
       <c r="G281" s="64"/>
@@ -16547,13 +16551,13 @@
         <v>49</v>
       </c>
       <c r="C282" s="62" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D282" s="61" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="E282" s="63" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="F282" s="64"/>
       <c r="G282" s="64"/>
@@ -16588,13 +16592,13 @@
         <v>49</v>
       </c>
       <c r="C283" s="62" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D283" s="61" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="E283" s="63" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="F283" s="64"/>
       <c r="G283" s="64"/>
@@ -16629,13 +16633,13 @@
         <v>49</v>
       </c>
       <c r="C284" s="62" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D284" s="61" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="E284" s="63" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F284" s="64"/>
       <c r="G284" s="64"/>
@@ -16670,13 +16674,13 @@
         <v>49</v>
       </c>
       <c r="C285" s="62" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D285" s="61" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="E285" s="63" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F285" s="64"/>
       <c r="G285" s="64"/>
@@ -16698,7 +16702,7 @@
       <c r="S285" s="66"/>
       <c r="T285" s="66"/>
       <c r="U285" s="67" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="V285" s="68"/>
       <c r="W285" s="66" t="s">
@@ -19417,42 +19421,42 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
   </sheetData>
@@ -19490,22 +19494,22 @@
   <sheetData>
     <row r="1" spans="1:7" customHeight="1" ht="14.25">
       <c r="A1" s="26" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="D1" s="72" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="G1" s="39" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="2" spans="1:7" customHeight="1" ht="14.25">
@@ -19513,13 +19517,13 @@
         <v>50</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C2" s="70" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="D2" s="73" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="3" spans="1:7" customHeight="1" ht="14.25">
@@ -19527,13 +19531,13 @@
         <v>59</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C3" s="70" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="D3" s="74" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="4" spans="1:7" customHeight="1" ht="14.25">
@@ -19541,55 +19545,55 @@
         <v>63</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C4" s="70" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="D4" s="75" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="5" spans="1:7" customHeight="1" ht="14.25">
       <c r="A5" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C5" s="70" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="D5" s="74" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="6" spans="1:7" customHeight="1" ht="14.25">
       <c r="A6" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C6" s="70" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="D6" s="75" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="7" spans="1:7" customHeight="1" ht="14.5">
       <c r="A7" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C7" s="70" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="D7" s="75" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="8" spans="1:7" customHeight="1" ht="14.5">
@@ -19597,13 +19601,13 @@
         <v>65</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C8" s="70" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="D8" s="75" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="9" spans="1:7" customHeight="1" ht="14.5">
@@ -19611,125 +19615,125 @@
         <v>61</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C9" s="70" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="D9" s="75" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="10" spans="1:7" customHeight="1" ht="43.5">
       <c r="A10" s="5" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C10" s="71" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="D10" s="74" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="11" spans="1:7" customHeight="1" ht="14.25">
       <c r="A11" s="5" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C11" s="70" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="D11" s="75" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="12" spans="1:7" customHeight="1" ht="14.25">
       <c r="A12" s="5" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C12" s="70" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="D12" s="75" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="13" spans="1:7" customHeight="1" ht="14.25">
       <c r="A13" s="5" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C13" s="70" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="D13" s="75" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="14" spans="1:7" customHeight="1" ht="14.25">
       <c r="A14" s="5" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C14" s="70" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="D14" s="75" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="15" spans="1:7" customHeight="1" ht="14.25">
       <c r="A15" s="5" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C15" s="70">
         <v>521</v>
       </c>
       <c r="D15" s="75" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="16" spans="1:7" customHeight="1" ht="14.25">
       <c r="A16" s="77" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C16" s="79" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D16" s="75" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="17" spans="1:7" customHeight="1" ht="14.25">
       <c r="A17" s="78" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B17" s="76" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C17" s="80" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="D17" s="75" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="18" spans="1:7" customHeight="1" ht="14.25"/>
@@ -20718,15 +20722,15 @@
     </row>
     <row r="2" spans="1:6" customHeight="1" ht="14.25">
       <c r="A2" s="4" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:6" customHeight="1" ht="14.25">
       <c r="A3" s="4" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>53</v>

--- a/GATEWAY/A1_111_DLABSRLXX/D.Lab_Srl/OsteoEasy/2.0/report-checklist.xlsx
+++ b/GATEWAY/A1_111_DLABSRLXX/D.Lab_Srl/OsteoEasy/2.0/report-checklist.xlsx
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="690">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="691">
   <si>
     <t>COME VALORIZZARE LA CHECKLIST (tab TestCases)</t>
   </si>
@@ -390,13 +390,13 @@
     <t>VALIDAZIONE_TOKEN_JWT_RSA_KO</t>
   </si>
   <si>
-    <t>03/04/2026</t>
-  </si>
-  <si>
-    <t>2026-04-03T08:55:57+02:00</t>
-  </si>
-  <si>
-    <t>e4cbe928d3367379bb29becc62b6a271</t>
+    <t>05/04/2026</t>
+  </si>
+  <si>
+    <t>2026-04-05T08:46:57+02:00</t>
+  </si>
+  <si>
+    <t>88bf7c33f18868fce0485eca4876ab6b</t>
   </si>
   <si>
     <t>SI</t>
@@ -495,7 +495,7 @@
     <t>VALIDAZIONE_TOKEN_JWT_CAMPO_RSA_KO</t>
   </si>
   <si>
-    <t>16dbcf2db05f5d236691d07bf272b2c6</t>
+    <t>b201314daf4f83715601977b9e69502e</t>
   </si>
   <si>
     <t>VALIDAZIONE_TOKEN_JWT_CAMPO_CERT_VAC_KO</t>
@@ -1115,13 +1115,10 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 6" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>2026-04-03T08:55:58+02:00</t>
-  </si>
-  <si>
-    <t>f3e8211741752326f40bcc70611a5d7d</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.eab7ea2a56^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>7f517833e20770b07a3f0623e6a39885</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.5f015d0e0a^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>Si e' verificato un errore durante l'operazione. Errore di validazione del documento CDA. Verificare il contenuto del documento e riprovare.</t>
@@ -1137,10 +1134,13 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 8" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>6290482be6ab3944900a533193ed8abf</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.771763e932^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>2026-04-05T08:46:58+02:00</t>
+  </si>
+  <si>
+    <t>1092d6abceb0441de8cfbfe88facd2c6</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.b20cca2eb1^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RSA_CT9_KO</t>
@@ -1150,10 +1150,10 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 9" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>8925a9a26e0f147bde4d645f633ddead</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.3bb4251d43^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>054985100ddf44df6df9f1c9d6c16e93</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.af0eb4c6b2^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RSA_CT10_KO</t>
@@ -1163,10 +1163,10 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 10" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>f957e6203e3bc87af35179f4b13dc90e</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.bbb899b1de^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>96875f4f4e866afee3915727f90c7a42</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.ab86552b27^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RSA_CT13_KO</t>
@@ -1176,13 +1176,10 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 13" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>2026-04-03T08:55:59+02:00</t>
-  </si>
-  <si>
-    <t>0771b01e0f1fb116377ee9fabd753bbe</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.186999bd77^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>60096d146e015f489b2771c5103dfe09</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.bdf0e8f941^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RSA_CT14_KO</t>
@@ -1192,10 +1189,13 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 14" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>a963b22cd7cde9192710f6d264da436d</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.f952ed1f3c^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>2026-04-05T08:46:59+02:00</t>
+  </si>
+  <si>
+    <t>328e36daff3472dac4eb0fe56fe0b0df</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.df6b701edb^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RSA_CT15_KO</t>
@@ -1205,10 +1205,10 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 15" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>c356c36d9fbab67b3c3dd59843b44948</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.708f92b7c0^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>b62f01005e616f4b1fc5d976b2f962c8</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.d463904d1a^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RSA_CT16_KO</t>
@@ -1218,13 +1218,10 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 16" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>2026-04-03T08:56:00+02:00</t>
-  </si>
-  <si>
-    <t>0fe3f7b3e99b578acb7586a39b845750</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.8127a1416d^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>d5282b07adbbafdc30fde7940853c973</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.7c9f07619c^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RSA_CT17_KO</t>
@@ -1234,10 +1231,13 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 17" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>84297aec955c9eeb4c911ae6ee49f45c</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.8517eaadda^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>2026-04-05T08:47:00+02:00</t>
+  </si>
+  <si>
+    <t>868e33bbc9f116edc69dbbfd497083cd</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.837218d61b^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RSA_CT18_KO</t>
@@ -1247,10 +1247,10 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 18" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>e7c274eb375320ce00e905f6fd2e1179</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.947422b0bd^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>1616926f49ab3696b95a50934a660430</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.9e36de85a4^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RSA_CT19_KO</t>
@@ -1260,10 +1260,10 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 19" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>26c5d1b3e06dd6238ab65cc62efa212a</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.3f1f3284c9^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>b5207f1e554cabf7de71323e5ab1bcf8</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.4892c59b6b^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RSA_CT20_KO</t>
@@ -1273,13 +1273,10 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 20" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>2026-04-03T08:56:01+02:00</t>
-  </si>
-  <si>
-    <t>4c1d170ce7f35b229c164970faa70921</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.641ed129c1^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>2eaa80c05d5d3583830b7fbec632313a</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.16906e0b9f^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RSA_CT21_KO</t>
@@ -1289,10 +1286,13 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 21" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>dd1dab393f5514349139f284b880a281</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.98cae7d745^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>2026-04-05T08:47:01+02:00</t>
+  </si>
+  <si>
+    <t>772e6ec254edf91b76be07fabf085a91</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.10a40ffacb^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RSA_CT22_KO</t>
@@ -1302,10 +1302,10 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 22" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>b4f2807e75d2cdd87b1ddb9b99ac29cd</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.8dca82b5dc^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>f607471fa5e4c99f38f1156d168aedb7</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.38f4f074e5^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RSA_CT23_KO</t>
@@ -1315,13 +1315,10 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 23" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>2026-04-03T08:56:02+02:00</t>
-  </si>
-  <si>
-    <t>4b4225c36393a2fde7ed1636fcd97d9d</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.4bb3c6cbab^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>4ca491aa09dd165273331f33e20ad8da</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.219f921d1e^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_PSS_CT6_KO</t>
@@ -1561,10 +1558,13 @@
 Il Documento CDA2 Referto Specialistica Ambulatoriale dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 24" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>9fc297b462711c6a0c93e0c394ac55bf</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.559394b32c^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>2026-04-05T08:46:56+02:00</t>
+  </si>
+  <si>
+    <t>69b5b697682013d3b62cde00d9e8959f</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.a02c4ac001^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RSA_CT25</t>
@@ -1574,10 +1574,10 @@
 Il Documento CDA2 Referto Specialistica Ambulatoriale dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 25" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>1c975a5d8d21a09f2fd72b0a1b1d84fd</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.12aad0cbef^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>c2772f9e9f4da061f179b08bd388ff91</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.009703c8bf^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_LDO_CT17</t>
@@ -1658,10 +1658,13 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 26" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>b418b517cbc0940ea77bd83e0012149b</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.29b5acc539^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>2026-04-05T08:47:02+02:00</t>
+  </si>
+  <si>
+    <t>ea53d60d79fd31be747333095e72cd49</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.7265ee8044^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RAD_CT24_KO</t>
@@ -1713,7 +1716,10 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 27" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>af819f8409c307f6c87a1bcbf6fe25d3</t>
+    <t>c6449c069a5d36a97530b4264d9c9422</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.1908eae4de^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_PSS_CT22_KO</t>
@@ -1765,13 +1771,10 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 28" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>2026-04-03T08:56:03+02:00</t>
-  </si>
-  <si>
-    <t>b1d4cdb3427cb7d71bd542bc5c93ee3c</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.6a844f08ee^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>0e83a642087369c79f47656fc09eea32</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.ab07c1eda2^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_PSS_CT23</t>
@@ -9375,13 +9378,13 @@
         <v>67</v>
       </c>
       <c r="G116" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="H116" s="31" t="s">
         <v>264</v>
       </c>
-      <c r="H116" s="31" t="s">
+      <c r="I116" s="36" t="s">
         <v>265</v>
-      </c>
-      <c r="I116" s="36" t="s">
-        <v>266</v>
       </c>
       <c r="J116" s="32" t="s">
         <v>70</v>
@@ -9395,7 +9398,7 @@
         <v>70</v>
       </c>
       <c r="O116" s="32" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P116" s="32" t="s">
         <v>53</v>
@@ -9407,7 +9410,7 @@
         <v>70</v>
       </c>
       <c r="S116" s="32" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="T116" s="32"/>
       <c r="U116" s="33"/>
@@ -9427,16 +9430,16 @@
         <v>65</v>
       </c>
       <c r="D117" s="29" t="s">
+        <v>268</v>
+      </c>
+      <c r="E117" s="37" t="s">
         <v>269</v>
-      </c>
-      <c r="E117" s="37" t="s">
-        <v>270</v>
       </c>
       <c r="F117" s="31" t="s">
         <v>67</v>
       </c>
       <c r="G117" s="31" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="H117" s="31" t="s">
         <v>271</v>
@@ -9456,7 +9459,7 @@
         <v>70</v>
       </c>
       <c r="O117" s="32" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P117" s="32" t="s">
         <v>53</v>
@@ -9468,7 +9471,7 @@
         <v>70</v>
       </c>
       <c r="S117" s="32" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="T117" s="32"/>
       <c r="U117" s="33"/>
@@ -9497,7 +9500,7 @@
         <v>67</v>
       </c>
       <c r="G118" s="31" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="H118" s="31" t="s">
         <v>275</v>
@@ -9517,7 +9520,7 @@
         <v>70</v>
       </c>
       <c r="O118" s="32" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P118" s="32" t="s">
         <v>53</v>
@@ -9529,7 +9532,7 @@
         <v>70</v>
       </c>
       <c r="S118" s="32" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="T118" s="32"/>
       <c r="U118" s="33"/>
@@ -9558,7 +9561,7 @@
         <v>67</v>
       </c>
       <c r="G119" s="31" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="H119" s="31" t="s">
         <v>279</v>
@@ -9578,7 +9581,7 @@
         <v>70</v>
       </c>
       <c r="O119" s="32" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P119" s="32" t="s">
         <v>53</v>
@@ -9590,7 +9593,7 @@
         <v>70</v>
       </c>
       <c r="S119" s="32" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="T119" s="32"/>
       <c r="U119" s="33"/>
@@ -9619,13 +9622,13 @@
         <v>67</v>
       </c>
       <c r="G120" s="31" t="s">
+        <v>270</v>
+      </c>
+      <c r="H120" s="31" t="s">
         <v>283</v>
       </c>
-      <c r="H120" s="31" t="s">
+      <c r="I120" s="36" t="s">
         <v>284</v>
-      </c>
-      <c r="I120" s="36" t="s">
-        <v>285</v>
       </c>
       <c r="J120" s="32" t="s">
         <v>70</v>
@@ -9639,7 +9642,7 @@
         <v>70</v>
       </c>
       <c r="O120" s="32" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P120" s="32" t="s">
         <v>53</v>
@@ -9651,7 +9654,7 @@
         <v>70</v>
       </c>
       <c r="S120" s="32" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="T120" s="32"/>
       <c r="U120" s="33"/>
@@ -9671,16 +9674,16 @@
         <v>65</v>
       </c>
       <c r="D121" s="29" t="s">
+        <v>285</v>
+      </c>
+      <c r="E121" s="37" t="s">
         <v>286</v>
-      </c>
-      <c r="E121" s="37" t="s">
-        <v>287</v>
       </c>
       <c r="F121" s="31" t="s">
         <v>67</v>
       </c>
       <c r="G121" s="31" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="H121" s="31" t="s">
         <v>288</v>
@@ -9700,7 +9703,7 @@
         <v>70</v>
       </c>
       <c r="O121" s="32" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P121" s="32" t="s">
         <v>53</v>
@@ -9712,7 +9715,7 @@
         <v>70</v>
       </c>
       <c r="S121" s="32" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="T121" s="32"/>
       <c r="U121" s="33"/>
@@ -9741,7 +9744,7 @@
         <v>67</v>
       </c>
       <c r="G122" s="31" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="H122" s="31" t="s">
         <v>292</v>
@@ -9761,7 +9764,7 @@
         <v>70</v>
       </c>
       <c r="O122" s="32" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P122" s="32" t="s">
         <v>53</v>
@@ -9773,7 +9776,7 @@
         <v>70</v>
       </c>
       <c r="S122" s="32" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="T122" s="32"/>
       <c r="U122" s="33"/>
@@ -9802,13 +9805,13 @@
         <v>67</v>
       </c>
       <c r="G123" s="31" t="s">
+        <v>287</v>
+      </c>
+      <c r="H123" s="31" t="s">
         <v>296</v>
       </c>
-      <c r="H123" s="31" t="s">
+      <c r="I123" s="36" t="s">
         <v>297</v>
-      </c>
-      <c r="I123" s="36" t="s">
-        <v>298</v>
       </c>
       <c r="J123" s="32" t="s">
         <v>70</v>
@@ -9822,7 +9825,7 @@
         <v>70</v>
       </c>
       <c r="O123" s="32" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P123" s="32" t="s">
         <v>53</v>
@@ -9834,7 +9837,7 @@
         <v>70</v>
       </c>
       <c r="S123" s="32" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="T123" s="32"/>
       <c r="U123" s="33"/>
@@ -9854,16 +9857,16 @@
         <v>65</v>
       </c>
       <c r="D124" s="29" t="s">
+        <v>298</v>
+      </c>
+      <c r="E124" s="37" t="s">
         <v>299</v>
-      </c>
-      <c r="E124" s="37" t="s">
-        <v>300</v>
       </c>
       <c r="F124" s="31" t="s">
         <v>67</v>
       </c>
       <c r="G124" s="31" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="H124" s="31" t="s">
         <v>301</v>
@@ -9883,7 +9886,7 @@
         <v>70</v>
       </c>
       <c r="O124" s="32" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P124" s="32" t="s">
         <v>53</v>
@@ -9895,7 +9898,7 @@
         <v>70</v>
       </c>
       <c r="S124" s="32" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="T124" s="32"/>
       <c r="U124" s="33"/>
@@ -9924,7 +9927,7 @@
         <v>67</v>
       </c>
       <c r="G125" s="31" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="H125" s="31" t="s">
         <v>305</v>
@@ -9944,7 +9947,7 @@
         <v>70</v>
       </c>
       <c r="O125" s="32" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P125" s="32" t="s">
         <v>53</v>
@@ -9956,7 +9959,7 @@
         <v>70</v>
       </c>
       <c r="S125" s="32" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="T125" s="32"/>
       <c r="U125" s="33"/>
@@ -9985,7 +9988,7 @@
         <v>67</v>
       </c>
       <c r="G126" s="31" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="H126" s="31" t="s">
         <v>309</v>
@@ -10005,7 +10008,7 @@
         <v>70</v>
       </c>
       <c r="O126" s="32" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P126" s="32" t="s">
         <v>53</v>
@@ -10017,7 +10020,7 @@
         <v>70</v>
       </c>
       <c r="S126" s="32" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="T126" s="32"/>
       <c r="U126" s="33"/>
@@ -10046,13 +10049,13 @@
         <v>67</v>
       </c>
       <c r="G127" s="31" t="s">
+        <v>300</v>
+      </c>
+      <c r="H127" s="31" t="s">
         <v>313</v>
       </c>
-      <c r="H127" s="31" t="s">
+      <c r="I127" s="36" t="s">
         <v>314</v>
-      </c>
-      <c r="I127" s="36" t="s">
-        <v>315</v>
       </c>
       <c r="J127" s="32" t="s">
         <v>70</v>
@@ -10066,7 +10069,7 @@
         <v>70</v>
       </c>
       <c r="O127" s="32" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P127" s="32" t="s">
         <v>53</v>
@@ -10078,7 +10081,7 @@
         <v>70</v>
       </c>
       <c r="S127" s="32" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="T127" s="32"/>
       <c r="U127" s="33"/>
@@ -10098,16 +10101,16 @@
         <v>65</v>
       </c>
       <c r="D128" s="29" t="s">
+        <v>315</v>
+      </c>
+      <c r="E128" s="37" t="s">
         <v>316</v>
-      </c>
-      <c r="E128" s="37" t="s">
-        <v>317</v>
       </c>
       <c r="F128" s="31" t="s">
         <v>67</v>
       </c>
       <c r="G128" s="31" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="H128" s="31" t="s">
         <v>318</v>
@@ -10127,7 +10130,7 @@
         <v>70</v>
       </c>
       <c r="O128" s="32" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P128" s="32" t="s">
         <v>53</v>
@@ -10139,7 +10142,7 @@
         <v>70</v>
       </c>
       <c r="S128" s="32" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="T128" s="32"/>
       <c r="U128" s="33"/>
@@ -10168,7 +10171,7 @@
         <v>67</v>
       </c>
       <c r="G129" s="31" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="H129" s="31" t="s">
         <v>322</v>
@@ -10188,7 +10191,7 @@
         <v>70</v>
       </c>
       <c r="O129" s="32" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P129" s="32" t="s">
         <v>53</v>
@@ -10200,7 +10203,7 @@
         <v>70</v>
       </c>
       <c r="S129" s="32" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="T129" s="32"/>
       <c r="U129" s="33"/>
@@ -10229,13 +10232,13 @@
         <v>67</v>
       </c>
       <c r="G130" s="31" t="s">
+        <v>317</v>
+      </c>
+      <c r="H130" s="31" t="s">
         <v>326</v>
       </c>
-      <c r="H130" s="31" t="s">
+      <c r="I130" s="36" t="s">
         <v>327</v>
-      </c>
-      <c r="I130" s="36" t="s">
-        <v>328</v>
       </c>
       <c r="J130" s="32" t="s">
         <v>70</v>
@@ -10249,7 +10252,7 @@
         <v>70</v>
       </c>
       <c r="O130" s="32" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P130" s="32" t="s">
         <v>53</v>
@@ -10261,7 +10264,7 @@
         <v>70</v>
       </c>
       <c r="S130" s="32" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="T130" s="32"/>
       <c r="U130" s="33"/>
@@ -10281,10 +10284,10 @@
         <v>61</v>
       </c>
       <c r="D131" s="29" t="s">
+        <v>328</v>
+      </c>
+      <c r="E131" s="37" t="s">
         <v>329</v>
-      </c>
-      <c r="E131" s="37" t="s">
-        <v>330</v>
       </c>
       <c r="F131" s="31"/>
       <c r="G131" s="31"/>
@@ -10322,10 +10325,10 @@
         <v>61</v>
       </c>
       <c r="D132" s="29" t="s">
+        <v>330</v>
+      </c>
+      <c r="E132" s="37" t="s">
         <v>331</v>
-      </c>
-      <c r="E132" s="37" t="s">
-        <v>332</v>
       </c>
       <c r="F132" s="31"/>
       <c r="G132" s="31"/>
@@ -10363,10 +10366,10 @@
         <v>61</v>
       </c>
       <c r="D133" s="29" t="s">
+        <v>332</v>
+      </c>
+      <c r="E133" s="37" t="s">
         <v>333</v>
-      </c>
-      <c r="E133" s="37" t="s">
-        <v>334</v>
       </c>
       <c r="F133" s="31"/>
       <c r="G133" s="31"/>
@@ -10404,10 +10407,10 @@
         <v>61</v>
       </c>
       <c r="D134" s="29" t="s">
+        <v>334</v>
+      </c>
+      <c r="E134" s="37" t="s">
         <v>335</v>
-      </c>
-      <c r="E134" s="37" t="s">
-        <v>336</v>
       </c>
       <c r="F134" s="31"/>
       <c r="G134" s="31"/>
@@ -10445,10 +10448,10 @@
         <v>61</v>
       </c>
       <c r="D135" s="29" t="s">
+        <v>336</v>
+      </c>
+      <c r="E135" s="37" t="s">
         <v>337</v>
-      </c>
-      <c r="E135" s="37" t="s">
-        <v>338</v>
       </c>
       <c r="F135" s="31"/>
       <c r="G135" s="31"/>
@@ -10486,10 +10489,10 @@
         <v>61</v>
       </c>
       <c r="D136" s="29" t="s">
+        <v>338</v>
+      </c>
+      <c r="E136" s="37" t="s">
         <v>339</v>
-      </c>
-      <c r="E136" s="37" t="s">
-        <v>340</v>
       </c>
       <c r="F136" s="31"/>
       <c r="G136" s="31"/>
@@ -10527,10 +10530,10 @@
         <v>61</v>
       </c>
       <c r="D137" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="E137" s="37" t="s">
         <v>341</v>
-      </c>
-      <c r="E137" s="37" t="s">
-        <v>342</v>
       </c>
       <c r="F137" s="31"/>
       <c r="G137" s="31"/>
@@ -10568,10 +10571,10 @@
         <v>61</v>
       </c>
       <c r="D138" s="29" t="s">
+        <v>342</v>
+      </c>
+      <c r="E138" s="37" t="s">
         <v>343</v>
-      </c>
-      <c r="E138" s="37" t="s">
-        <v>344</v>
       </c>
       <c r="F138" s="31"/>
       <c r="G138" s="31"/>
@@ -10609,10 +10612,10 @@
         <v>61</v>
       </c>
       <c r="D139" s="29" t="s">
+        <v>344</v>
+      </c>
+      <c r="E139" s="37" t="s">
         <v>345</v>
-      </c>
-      <c r="E139" s="37" t="s">
-        <v>346</v>
       </c>
       <c r="F139" s="31"/>
       <c r="G139" s="31"/>
@@ -10650,10 +10653,10 @@
         <v>61</v>
       </c>
       <c r="D140" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="E140" s="37" t="s">
         <v>347</v>
-      </c>
-      <c r="E140" s="37" t="s">
-        <v>348</v>
       </c>
       <c r="F140" s="31"/>
       <c r="G140" s="31"/>
@@ -10691,10 +10694,10 @@
         <v>61</v>
       </c>
       <c r="D141" s="29" t="s">
+        <v>348</v>
+      </c>
+      <c r="E141" s="37" t="s">
         <v>349</v>
-      </c>
-      <c r="E141" s="37" t="s">
-        <v>350</v>
       </c>
       <c r="F141" s="31"/>
       <c r="G141" s="31"/>
@@ -10732,10 +10735,10 @@
         <v>61</v>
       </c>
       <c r="D142" s="29" t="s">
+        <v>350</v>
+      </c>
+      <c r="E142" s="37" t="s">
         <v>351</v>
-      </c>
-      <c r="E142" s="37" t="s">
-        <v>352</v>
       </c>
       <c r="F142" s="31"/>
       <c r="G142" s="31"/>
@@ -10773,10 +10776,10 @@
         <v>61</v>
       </c>
       <c r="D143" s="29" t="s">
+        <v>352</v>
+      </c>
+      <c r="E143" s="37" t="s">
         <v>353</v>
-      </c>
-      <c r="E143" s="37" t="s">
-        <v>354</v>
       </c>
       <c r="F143" s="31"/>
       <c r="G143" s="31"/>
@@ -10814,10 +10817,10 @@
         <v>61</v>
       </c>
       <c r="D144" s="29" t="s">
+        <v>354</v>
+      </c>
+      <c r="E144" s="37" t="s">
         <v>355</v>
-      </c>
-      <c r="E144" s="37" t="s">
-        <v>356</v>
       </c>
       <c r="F144" s="31"/>
       <c r="G144" s="31"/>
@@ -10855,10 +10858,10 @@
         <v>61</v>
       </c>
       <c r="D145" s="29" t="s">
+        <v>356</v>
+      </c>
+      <c r="E145" s="37" t="s">
         <v>357</v>
-      </c>
-      <c r="E145" s="37" t="s">
-        <v>358</v>
       </c>
       <c r="F145" s="31"/>
       <c r="G145" s="31"/>
@@ -10896,10 +10899,10 @@
         <v>50</v>
       </c>
       <c r="D146" s="29" t="s">
+        <v>358</v>
+      </c>
+      <c r="E146" s="37" t="s">
         <v>359</v>
-      </c>
-      <c r="E146" s="37" t="s">
-        <v>360</v>
       </c>
       <c r="F146" s="31"/>
       <c r="G146" s="31"/>
@@ -10937,10 +10940,10 @@
         <v>50</v>
       </c>
       <c r="D147" s="29" t="s">
+        <v>360</v>
+      </c>
+      <c r="E147" s="37" t="s">
         <v>361</v>
-      </c>
-      <c r="E147" s="37" t="s">
-        <v>362</v>
       </c>
       <c r="F147" s="31"/>
       <c r="G147" s="31"/>
@@ -10975,13 +10978,13 @@
         <v>49</v>
       </c>
       <c r="C148" s="35" t="s">
+        <v>362</v>
+      </c>
+      <c r="D148" s="29" t="s">
         <v>363</v>
       </c>
-      <c r="D148" s="29" t="s">
+      <c r="E148" s="37" t="s">
         <v>364</v>
-      </c>
-      <c r="E148" s="37" t="s">
-        <v>365</v>
       </c>
       <c r="F148" s="31"/>
       <c r="G148" s="31"/>
@@ -11016,13 +11019,13 @@
         <v>49</v>
       </c>
       <c r="C149" s="35" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D149" s="29" t="s">
+        <v>365</v>
+      </c>
+      <c r="E149" s="37" t="s">
         <v>366</v>
-      </c>
-      <c r="E149" s="37" t="s">
-        <v>367</v>
       </c>
       <c r="F149" s="31"/>
       <c r="G149" s="31"/>
@@ -11057,13 +11060,13 @@
         <v>49</v>
       </c>
       <c r="C150" s="35" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D150" s="29" t="s">
+        <v>367</v>
+      </c>
+      <c r="E150" s="37" t="s">
         <v>368</v>
-      </c>
-      <c r="E150" s="37" t="s">
-        <v>369</v>
       </c>
       <c r="F150" s="31"/>
       <c r="G150" s="31"/>
@@ -11098,10 +11101,10 @@
         <v>49</v>
       </c>
       <c r="C151" s="35" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D151" s="29" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E151" s="37" t="s">
         <v>57</v>
@@ -11139,10 +11142,10 @@
         <v>49</v>
       </c>
       <c r="C152" s="35" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D152" s="29" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E152" s="37" t="s">
         <v>80</v>
@@ -11180,13 +11183,13 @@
         <v>49</v>
       </c>
       <c r="C153" s="35" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D153" s="29" t="s">
+        <v>371</v>
+      </c>
+      <c r="E153" s="37" t="s">
         <v>372</v>
-      </c>
-      <c r="E153" s="37" t="s">
-        <v>373</v>
       </c>
       <c r="F153" s="31"/>
       <c r="G153" s="31"/>
@@ -11223,13 +11226,13 @@
         <v>49</v>
       </c>
       <c r="C154" s="35" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D154" s="29" t="s">
+        <v>373</v>
+      </c>
+      <c r="E154" s="37" t="s">
         <v>374</v>
-      </c>
-      <c r="E154" s="37" t="s">
-        <v>375</v>
       </c>
       <c r="F154" s="31"/>
       <c r="G154" s="31"/>
@@ -11264,13 +11267,13 @@
         <v>49</v>
       </c>
       <c r="C155" s="35" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D155" s="29" t="s">
+        <v>375</v>
+      </c>
+      <c r="E155" s="37" t="s">
         <v>376</v>
-      </c>
-      <c r="E155" s="37" t="s">
-        <v>377</v>
       </c>
       <c r="F155" s="31"/>
       <c r="G155" s="31"/>
@@ -11305,13 +11308,13 @@
         <v>49</v>
       </c>
       <c r="C156" s="35" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D156" s="29" t="s">
+        <v>377</v>
+      </c>
+      <c r="E156" s="37" t="s">
         <v>378</v>
-      </c>
-      <c r="E156" s="37" t="s">
-        <v>379</v>
       </c>
       <c r="F156" s="31"/>
       <c r="G156" s="31"/>
@@ -11346,13 +11349,13 @@
         <v>49</v>
       </c>
       <c r="C157" s="35" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D157" s="29" t="s">
+        <v>379</v>
+      </c>
+      <c r="E157" s="37" t="s">
         <v>380</v>
-      </c>
-      <c r="E157" s="37" t="s">
-        <v>381</v>
       </c>
       <c r="F157" s="31"/>
       <c r="G157" s="31"/>
@@ -11387,13 +11390,13 @@
         <v>49</v>
       </c>
       <c r="C158" s="35" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D158" s="29" t="s">
+        <v>381</v>
+      </c>
+      <c r="E158" s="37" t="s">
         <v>382</v>
-      </c>
-      <c r="E158" s="37" t="s">
-        <v>383</v>
       </c>
       <c r="F158" s="31"/>
       <c r="G158" s="31"/>
@@ -11428,13 +11431,13 @@
         <v>49</v>
       </c>
       <c r="C159" s="35" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D159" s="29" t="s">
+        <v>383</v>
+      </c>
+      <c r="E159" s="37" t="s">
         <v>384</v>
-      </c>
-      <c r="E159" s="37" t="s">
-        <v>385</v>
       </c>
       <c r="F159" s="31"/>
       <c r="G159" s="31"/>
@@ -11469,13 +11472,13 @@
         <v>49</v>
       </c>
       <c r="C160" s="35" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D160" s="29" t="s">
+        <v>385</v>
+      </c>
+      <c r="E160" s="37" t="s">
         <v>386</v>
-      </c>
-      <c r="E160" s="37" t="s">
-        <v>387</v>
       </c>
       <c r="F160" s="31"/>
       <c r="G160" s="31"/>
@@ -11510,13 +11513,13 @@
         <v>49</v>
       </c>
       <c r="C161" s="35" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D161" s="29" t="s">
+        <v>387</v>
+      </c>
+      <c r="E161" s="37" t="s">
         <v>388</v>
-      </c>
-      <c r="E161" s="37" t="s">
-        <v>389</v>
       </c>
       <c r="F161" s="31"/>
       <c r="G161" s="31"/>
@@ -11551,13 +11554,13 @@
         <v>49</v>
       </c>
       <c r="C162" s="35" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D162" s="29" t="s">
+        <v>389</v>
+      </c>
+      <c r="E162" s="37" t="s">
         <v>390</v>
-      </c>
-      <c r="E162" s="37" t="s">
-        <v>391</v>
       </c>
       <c r="F162" s="31"/>
       <c r="G162" s="31"/>
@@ -11592,13 +11595,13 @@
         <v>49</v>
       </c>
       <c r="C163" s="35" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D163" s="29" t="s">
+        <v>391</v>
+      </c>
+      <c r="E163" s="37" t="s">
         <v>392</v>
-      </c>
-      <c r="E163" s="37" t="s">
-        <v>393</v>
       </c>
       <c r="F163" s="31"/>
       <c r="G163" s="31"/>
@@ -11636,16 +11639,16 @@
         <v>65</v>
       </c>
       <c r="D164" s="29" t="s">
+        <v>393</v>
+      </c>
+      <c r="E164" s="37" t="s">
         <v>394</v>
-      </c>
-      <c r="E164" s="37" t="s">
-        <v>395</v>
       </c>
       <c r="F164" s="31" t="s">
         <v>67</v>
       </c>
       <c r="G164" s="31" t="s">
-        <v>68</v>
+        <v>395</v>
       </c>
       <c r="H164" s="31" t="s">
         <v>396</v>
@@ -12096,7 +12099,7 @@
         <v>49</v>
       </c>
       <c r="C175" s="35" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D175" s="29" t="s">
         <v>420</v>
@@ -12149,13 +12152,13 @@
         <v>67</v>
       </c>
       <c r="G176" s="29" t="s">
-        <v>326</v>
+        <v>424</v>
       </c>
       <c r="H176" s="29" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="I176" s="29" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="J176" s="32" t="s">
         <v>70</v>
@@ -12169,7 +12172,7 @@
         <v>70</v>
       </c>
       <c r="O176" s="29" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P176" s="32" t="s">
         <v>53</v>
@@ -12181,7 +12184,7 @@
         <v>70</v>
       </c>
       <c r="S176" s="29" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="T176" s="32"/>
       <c r="U176" s="29"/>
@@ -12201,10 +12204,10 @@
         <v>63</v>
       </c>
       <c r="D177" s="29" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E177" s="37" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F177" s="29"/>
       <c r="G177" s="29"/>
@@ -12242,10 +12245,10 @@
         <v>77</v>
       </c>
       <c r="D178" s="29" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E178" s="37" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F178" s="29"/>
       <c r="G178" s="29"/>
@@ -12283,10 +12286,10 @@
         <v>73</v>
       </c>
       <c r="D179" s="29" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E179" s="37" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F179" s="29"/>
       <c r="G179" s="29"/>
@@ -12324,10 +12327,10 @@
         <v>75</v>
       </c>
       <c r="D180" s="29" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E180" s="37" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F180" s="29"/>
       <c r="G180" s="29"/>
@@ -12365,10 +12368,10 @@
         <v>50</v>
       </c>
       <c r="D181" s="29" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E181" s="37" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F181" s="29"/>
       <c r="G181" s="29"/>
@@ -12406,10 +12409,10 @@
         <v>59</v>
       </c>
       <c r="D182" s="29" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E182" s="37" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F182" s="29"/>
       <c r="G182" s="29"/>
@@ -12447,21 +12450,23 @@
         <v>65</v>
       </c>
       <c r="D183" s="29" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E183" s="37" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F183" s="29" t="s">
         <v>67</v>
       </c>
       <c r="G183" s="29" t="s">
-        <v>326</v>
+        <v>424</v>
       </c>
       <c r="H183" s="29" t="s">
-        <v>440</v>
-      </c>
-      <c r="I183" s="29"/>
+        <v>441</v>
+      </c>
+      <c r="I183" s="29" t="s">
+        <v>442</v>
+      </c>
       <c r="J183" s="32" t="s">
         <v>70</v>
       </c>
@@ -12474,7 +12479,7 @@
         <v>70</v>
       </c>
       <c r="O183" s="29" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P183" s="32" t="s">
         <v>53</v>
@@ -12486,7 +12491,7 @@
         <v>70</v>
       </c>
       <c r="S183" s="29" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="T183" s="32"/>
       <c r="U183" s="29"/>
@@ -12506,10 +12511,10 @@
         <v>61</v>
       </c>
       <c r="D184" s="29" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E184" s="37" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="F184" s="29"/>
       <c r="G184" s="29"/>
@@ -12544,13 +12549,13 @@
         <v>49</v>
       </c>
       <c r="C185" s="35" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D185" s="29" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E185" s="37" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F185" s="29"/>
       <c r="G185" s="29"/>
@@ -12588,10 +12593,10 @@
         <v>63</v>
       </c>
       <c r="D186" s="29" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="E186" s="37" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="F186" s="31"/>
       <c r="G186" s="31"/>
@@ -12629,10 +12634,10 @@
         <v>63</v>
       </c>
       <c r="D187" s="29" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="E187" s="37" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="F187" s="31"/>
       <c r="G187" s="31"/>
@@ -12670,10 +12675,10 @@
         <v>50</v>
       </c>
       <c r="D188" s="35" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E188" s="37" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="F188" s="31"/>
       <c r="G188" s="31"/>
@@ -12711,10 +12716,10 @@
         <v>63</v>
       </c>
       <c r="D189" s="29" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E189" s="37" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="F189" s="31"/>
       <c r="G189" s="31"/>
@@ -12752,22 +12757,22 @@
         <v>65</v>
       </c>
       <c r="D190" s="29" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E190" s="37" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="F190" s="31" t="s">
         <v>67</v>
       </c>
       <c r="G190" s="31" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="H190" s="31" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="I190" s="36" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="J190" s="32" t="s">
         <v>70</v>
@@ -12781,7 +12786,7 @@
         <v>70</v>
       </c>
       <c r="O190" s="32" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P190" s="32" t="s">
         <v>53</v>
@@ -12793,7 +12798,7 @@
         <v>70</v>
       </c>
       <c r="S190" s="32" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="T190" s="32"/>
       <c r="U190" s="33"/>
@@ -12813,10 +12818,10 @@
         <v>61</v>
       </c>
       <c r="D191" s="29" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E191" s="37" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F191" s="31"/>
       <c r="G191" s="31"/>
@@ -12854,10 +12859,10 @@
         <v>61</v>
       </c>
       <c r="D192" s="29" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E192" s="37" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F192" s="31"/>
       <c r="G192" s="31"/>
@@ -12895,10 +12900,10 @@
         <v>61</v>
       </c>
       <c r="D193" s="29" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E193" s="40" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F193" s="31"/>
       <c r="G193" s="31"/>
@@ -12933,13 +12938,13 @@
         <v>49</v>
       </c>
       <c r="C194" s="35" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D194" s="29" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E194" s="40" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="F194" s="31"/>
       <c r="G194" s="31"/>
@@ -12974,13 +12979,13 @@
         <v>49</v>
       </c>
       <c r="C195" s="35" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D195" s="29" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E195" s="40" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F195" s="31"/>
       <c r="G195" s="31"/>
@@ -13015,13 +13020,13 @@
         <v>49</v>
       </c>
       <c r="C196" s="35" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D196" s="29" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E196" s="40" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F196" s="31"/>
       <c r="G196" s="31"/>
@@ -13056,13 +13061,13 @@
         <v>49</v>
       </c>
       <c r="C197" s="35" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D197" s="29" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E197" s="40" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F197" s="31"/>
       <c r="G197" s="31"/>
@@ -13097,13 +13102,13 @@
         <v>49</v>
       </c>
       <c r="C198" s="35" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D198" s="29" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E198" s="40" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F198" s="31"/>
       <c r="G198" s="31"/>
@@ -13138,13 +13143,13 @@
         <v>49</v>
       </c>
       <c r="C199" s="35" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D199" s="29" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E199" s="40" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F199" s="31"/>
       <c r="G199" s="31"/>
@@ -13179,13 +13184,13 @@
         <v>49</v>
       </c>
       <c r="C200" s="35" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D200" s="29" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E200" s="40" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F200" s="31"/>
       <c r="G200" s="31"/>
@@ -13220,13 +13225,13 @@
         <v>49</v>
       </c>
       <c r="C201" s="35" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D201" s="29" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E201" s="40" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F201" s="31"/>
       <c r="G201" s="31"/>
@@ -13261,13 +13266,13 @@
         <v>49</v>
       </c>
       <c r="C202" s="35" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D202" s="29" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E202" s="40" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F202" s="31"/>
       <c r="G202" s="31"/>
@@ -13302,13 +13307,13 @@
         <v>49</v>
       </c>
       <c r="C203" s="35" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D203" s="29" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E203" s="40" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F203" s="31"/>
       <c r="G203" s="31"/>
@@ -13343,10 +13348,10 @@
         <v>49</v>
       </c>
       <c r="C204" s="35" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D204" s="29" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E204" s="37" t="s">
         <v>80</v>
@@ -13384,10 +13389,10 @@
         <v>49</v>
       </c>
       <c r="C205" s="35" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D205" s="29" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E205" s="37" t="s">
         <v>90</v>
@@ -13427,13 +13432,13 @@
         <v>49</v>
       </c>
       <c r="C206" s="35" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D206" s="29" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E206" s="40" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F206" s="31"/>
       <c r="G206" s="31"/>
@@ -13468,13 +13473,13 @@
         <v>49</v>
       </c>
       <c r="C207" s="35" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D207" s="29" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E207" s="40" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F207" s="31"/>
       <c r="G207" s="31"/>
@@ -13509,13 +13514,13 @@
         <v>49</v>
       </c>
       <c r="C208" s="35" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D208" s="29" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E208" s="40" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F208" s="31"/>
       <c r="G208" s="31"/>
@@ -13550,13 +13555,13 @@
         <v>49</v>
       </c>
       <c r="C209" s="35" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D209" s="29" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E209" s="40" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F209" s="31"/>
       <c r="G209" s="31"/>
@@ -13591,13 +13596,13 @@
         <v>49</v>
       </c>
       <c r="C210" s="35" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D210" s="29" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E210" s="40" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F210" s="31"/>
       <c r="G210" s="31"/>
@@ -13632,13 +13637,13 @@
         <v>49</v>
       </c>
       <c r="C211" s="35" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D211" s="29" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E211" s="40" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F211" s="31"/>
       <c r="G211" s="31"/>
@@ -13673,13 +13678,13 @@
         <v>49</v>
       </c>
       <c r="C212" s="35" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D212" s="29" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E212" s="40" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F212" s="31"/>
       <c r="G212" s="31"/>
@@ -13714,13 +13719,13 @@
         <v>49</v>
       </c>
       <c r="C213" s="35" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D213" s="29" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E213" s="40" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F213" s="31"/>
       <c r="G213" s="31"/>
@@ -13755,13 +13760,13 @@
         <v>49</v>
       </c>
       <c r="C214" s="35" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D214" s="29" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E214" s="40" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F214" s="31"/>
       <c r="G214" s="31"/>
@@ -13796,13 +13801,13 @@
         <v>49</v>
       </c>
       <c r="C215" s="35" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D215" s="29" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E215" s="40" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F215" s="31"/>
       <c r="G215" s="31"/>
@@ -13837,13 +13842,13 @@
         <v>49</v>
       </c>
       <c r="C216" s="35" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D216" s="29" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E216" s="40" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F216" s="31"/>
       <c r="G216" s="31"/>
@@ -13878,13 +13883,13 @@
         <v>49</v>
       </c>
       <c r="C217" s="35" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D217" s="29" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E217" s="40" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F217" s="31"/>
       <c r="G217" s="31"/>
@@ -13919,13 +13924,13 @@
         <v>49</v>
       </c>
       <c r="C218" s="35" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D218" s="29" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E218" s="40" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F218" s="31"/>
       <c r="G218" s="31"/>
@@ -13960,10 +13965,10 @@
         <v>49</v>
       </c>
       <c r="C219" s="35" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D219" s="29" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E219" s="37" t="s">
         <v>80</v>
@@ -14001,10 +14006,10 @@
         <v>49</v>
       </c>
       <c r="C220" s="35" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D220" s="29" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E220" s="37" t="s">
         <v>90</v>
@@ -14044,13 +14049,13 @@
         <v>49</v>
       </c>
       <c r="C221" s="35" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D221" s="29" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E221" s="40" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F221" s="31"/>
       <c r="G221" s="31"/>
@@ -14085,13 +14090,13 @@
         <v>49</v>
       </c>
       <c r="C222" s="35" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D222" s="29" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="E222" s="40" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F222" s="31"/>
       <c r="G222" s="31"/>
@@ -14126,13 +14131,13 @@
         <v>49</v>
       </c>
       <c r="C223" s="35" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D223" s="29" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E223" s="40" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="F223" s="31"/>
       <c r="G223" s="31"/>
@@ -14167,13 +14172,13 @@
         <v>49</v>
       </c>
       <c r="C224" s="35" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D224" s="29" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E224" s="40" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F224" s="31"/>
       <c r="G224" s="31"/>
@@ -14208,13 +14213,13 @@
         <v>49</v>
       </c>
       <c r="C225" s="35" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D225" s="29" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E225" s="40" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="F225" s="31"/>
       <c r="G225" s="31"/>
@@ -14249,13 +14254,13 @@
         <v>49</v>
       </c>
       <c r="C226" s="35" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D226" s="29" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E226" s="40" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F226" s="31"/>
       <c r="G226" s="31"/>
@@ -14290,13 +14295,13 @@
         <v>49</v>
       </c>
       <c r="C227" s="35" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D227" s="29" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E227" s="40" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F227" s="31"/>
       <c r="G227" s="31"/>
@@ -14331,13 +14336,13 @@
         <v>49</v>
       </c>
       <c r="C228" s="35" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D228" s="29" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E228" s="40" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F228" s="31"/>
       <c r="G228" s="31"/>
@@ -14372,13 +14377,13 @@
         <v>49</v>
       </c>
       <c r="C229" s="35" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D229" s="29" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E229" s="40" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F229" s="31"/>
       <c r="G229" s="31"/>
@@ -14413,13 +14418,13 @@
         <v>49</v>
       </c>
       <c r="C230" s="35" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D230" s="29" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E230" s="40" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F230" s="31"/>
       <c r="G230" s="31"/>
@@ -14454,13 +14459,13 @@
         <v>49</v>
       </c>
       <c r="C231" s="35" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D231" s="29" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E231" s="40" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F231" s="31"/>
       <c r="G231" s="31"/>
@@ -14495,13 +14500,13 @@
         <v>49</v>
       </c>
       <c r="C232" s="35" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D232" s="29" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E232" s="40" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="F232" s="31"/>
       <c r="G232" s="31"/>
@@ -14536,13 +14541,13 @@
         <v>49</v>
       </c>
       <c r="C233" s="35" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D233" s="29" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E233" s="40" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F233" s="31"/>
       <c r="G233" s="31"/>
@@ -14577,10 +14582,10 @@
         <v>49</v>
       </c>
       <c r="C234" s="35" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D234" s="29" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E234" s="37" t="s">
         <v>80</v>
@@ -14618,10 +14623,10 @@
         <v>49</v>
       </c>
       <c r="C235" s="35" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D235" s="29" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E235" s="37" t="s">
         <v>90</v>
@@ -14661,13 +14666,13 @@
         <v>49</v>
       </c>
       <c r="C236" s="42" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D236" s="41" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E236" s="40" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F236" s="43"/>
       <c r="G236" s="43"/>
@@ -14702,13 +14707,13 @@
         <v>49</v>
       </c>
       <c r="C237" s="42" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D237" s="41" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E237" s="40" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F237" s="43"/>
       <c r="G237" s="43"/>
@@ -14743,13 +14748,13 @@
         <v>49</v>
       </c>
       <c r="C238" s="42" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D238" s="41" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E238" s="40" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="F238" s="43"/>
       <c r="G238" s="43"/>
@@ -14784,13 +14789,13 @@
         <v>49</v>
       </c>
       <c r="C239" s="42" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D239" s="41" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E239" s="40" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F239" s="43"/>
       <c r="G239" s="43"/>
@@ -14825,13 +14830,13 @@
         <v>49</v>
       </c>
       <c r="C240" s="42" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D240" s="41" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E240" s="40" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="F240" s="43"/>
       <c r="G240" s="43"/>
@@ -14866,13 +14871,13 @@
         <v>49</v>
       </c>
       <c r="C241" s="42" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D241" s="41" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="E241" s="40" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="F241" s="43"/>
       <c r="G241" s="43"/>
@@ -14907,13 +14912,13 @@
         <v>49</v>
       </c>
       <c r="C242" s="42" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D242" s="41" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E242" s="40" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F242" s="43"/>
       <c r="G242" s="43"/>
@@ -14948,13 +14953,13 @@
         <v>49</v>
       </c>
       <c r="C243" s="42" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D243" s="41" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E243" s="40" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="F243" s="43"/>
       <c r="G243" s="43"/>
@@ -14989,10 +14994,10 @@
         <v>49</v>
       </c>
       <c r="C244" s="42" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D244" s="41" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E244" s="40" t="s">
         <v>80</v>
@@ -15030,10 +15035,10 @@
         <v>49</v>
       </c>
       <c r="C245" s="42" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D245" s="41" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E245" s="40" t="s">
         <v>90</v>
@@ -15073,13 +15078,13 @@
         <v>49</v>
       </c>
       <c r="C246" s="62" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D246" s="61" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E246" s="63" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="F246" s="64"/>
       <c r="G246" s="64"/>
@@ -15114,13 +15119,13 @@
         <v>49</v>
       </c>
       <c r="C247" s="62" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D247" s="61" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E247" s="63" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="F247" s="64"/>
       <c r="G247" s="64"/>
@@ -15155,13 +15160,13 @@
         <v>49</v>
       </c>
       <c r="C248" s="62" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D248" s="61" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E248" s="63" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="F248" s="64"/>
       <c r="G248" s="64"/>
@@ -15196,13 +15201,13 @@
         <v>49</v>
       </c>
       <c r="C249" s="62" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D249" s="61" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E249" s="63" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="F249" s="64"/>
       <c r="G249" s="64"/>
@@ -15237,13 +15242,13 @@
         <v>49</v>
       </c>
       <c r="C250" s="62" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D250" s="61" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E250" s="63" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="F250" s="64"/>
       <c r="G250" s="64"/>
@@ -15278,13 +15283,13 @@
         <v>49</v>
       </c>
       <c r="C251" s="62" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D251" s="61" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="E251" s="63" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="F251" s="64"/>
       <c r="G251" s="64"/>
@@ -15319,13 +15324,13 @@
         <v>49</v>
       </c>
       <c r="C252" s="62" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D252" s="61" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E252" s="63" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F252" s="64"/>
       <c r="G252" s="64"/>
@@ -15360,13 +15365,13 @@
         <v>49</v>
       </c>
       <c r="C253" s="62" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D253" s="61" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E253" s="63" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="F253" s="64"/>
       <c r="G253" s="64"/>
@@ -15401,13 +15406,13 @@
         <v>49</v>
       </c>
       <c r="C254" s="62" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D254" s="61" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E254" s="63" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="F254" s="64"/>
       <c r="G254" s="64"/>
@@ -15442,13 +15447,13 @@
         <v>49</v>
       </c>
       <c r="C255" s="62" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D255" s="61" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E255" s="63" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F255" s="64"/>
       <c r="G255" s="64"/>
@@ -15483,13 +15488,13 @@
         <v>49</v>
       </c>
       <c r="C256" s="62" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D256" s="61" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E256" s="63" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F256" s="64"/>
       <c r="G256" s="64"/>
@@ -15524,13 +15529,13 @@
         <v>49</v>
       </c>
       <c r="C257" s="62" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D257" s="61" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E257" s="63" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="F257" s="64"/>
       <c r="G257" s="64"/>
@@ -15565,13 +15570,13 @@
         <v>49</v>
       </c>
       <c r="C258" s="62" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D258" s="61" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E258" s="63" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="F258" s="64"/>
       <c r="G258" s="64"/>
@@ -15606,13 +15611,13 @@
         <v>49</v>
       </c>
       <c r="C259" s="62" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D259" s="61" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E259" s="63" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="F259" s="64"/>
       <c r="G259" s="64"/>
@@ -15647,13 +15652,13 @@
         <v>49</v>
       </c>
       <c r="C260" s="62" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D260" s="61" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E260" s="63" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="F260" s="64"/>
       <c r="G260" s="64"/>
@@ -15688,13 +15693,13 @@
         <v>49</v>
       </c>
       <c r="C261" s="62" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D261" s="61" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E261" s="63" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="F261" s="64"/>
       <c r="G261" s="64"/>
@@ -15729,13 +15734,13 @@
         <v>49</v>
       </c>
       <c r="C262" s="62" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D262" s="61" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E262" s="63" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="F262" s="64"/>
       <c r="G262" s="64"/>
@@ -15770,13 +15775,13 @@
         <v>49</v>
       </c>
       <c r="C263" s="62" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D263" s="61" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E263" s="63" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F263" s="64"/>
       <c r="G263" s="64"/>
@@ -15811,10 +15816,10 @@
         <v>49</v>
       </c>
       <c r="C264" s="62" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D264" s="61" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E264" s="63" t="s">
         <v>80</v>
@@ -15852,10 +15857,10 @@
         <v>49</v>
       </c>
       <c r="C265" s="62" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D265" s="61" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E265" s="63" t="s">
         <v>90</v>
@@ -15895,13 +15900,13 @@
         <v>49</v>
       </c>
       <c r="C266" s="62" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D266" s="61" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E266" s="63" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F266" s="64"/>
       <c r="G266" s="64"/>
@@ -15936,13 +15941,13 @@
         <v>49</v>
       </c>
       <c r="C267" s="62" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D267" s="61" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E267" s="63" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F267" s="64"/>
       <c r="G267" s="64"/>
@@ -15977,13 +15982,13 @@
         <v>49</v>
       </c>
       <c r="C268" s="62" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D268" s="61" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E268" s="63" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="F268" s="64"/>
       <c r="G268" s="64"/>
@@ -16018,13 +16023,13 @@
         <v>49</v>
       </c>
       <c r="C269" s="62" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D269" s="61" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="E269" s="63" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F269" s="64"/>
       <c r="G269" s="64"/>
@@ -16059,13 +16064,13 @@
         <v>49</v>
       </c>
       <c r="C270" s="62" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D270" s="61" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E270" s="63" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="F270" s="64"/>
       <c r="G270" s="64"/>
@@ -16100,13 +16105,13 @@
         <v>49</v>
       </c>
       <c r="C271" s="62" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D271" s="61" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="E271" s="63" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="F271" s="64"/>
       <c r="G271" s="64"/>
@@ -16141,13 +16146,13 @@
         <v>49</v>
       </c>
       <c r="C272" s="62" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D272" s="61" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="E272" s="63" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="F272" s="64"/>
       <c r="G272" s="64"/>
@@ -16182,13 +16187,13 @@
         <v>49</v>
       </c>
       <c r="C273" s="62" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D273" s="61" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="E273" s="63" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="F273" s="64"/>
       <c r="G273" s="64"/>
@@ -16223,13 +16228,13 @@
         <v>49</v>
       </c>
       <c r="C274" s="62" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D274" s="61" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="E274" s="63" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="F274" s="64"/>
       <c r="G274" s="64"/>
@@ -16264,13 +16269,13 @@
         <v>49</v>
       </c>
       <c r="C275" s="62" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D275" s="61" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="E275" s="63" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F275" s="64"/>
       <c r="G275" s="64"/>
@@ -16305,13 +16310,13 @@
         <v>49</v>
       </c>
       <c r="C276" s="62" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D276" s="61" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E276" s="63" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F276" s="64"/>
       <c r="G276" s="64"/>
@@ -16346,13 +16351,13 @@
         <v>49</v>
       </c>
       <c r="C277" s="62" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D277" s="61" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E277" s="63" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F277" s="64"/>
       <c r="G277" s="64"/>
@@ -16387,13 +16392,13 @@
         <v>49</v>
       </c>
       <c r="C278" s="62" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D278" s="61" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="E278" s="63" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="F278" s="64"/>
       <c r="G278" s="64"/>
@@ -16428,13 +16433,13 @@
         <v>49</v>
       </c>
       <c r="C279" s="62" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D279" s="61" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E279" s="63" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="F279" s="64"/>
       <c r="G279" s="64"/>
@@ -16469,13 +16474,13 @@
         <v>49</v>
       </c>
       <c r="C280" s="62" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D280" s="61" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E280" s="63" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="F280" s="64"/>
       <c r="G280" s="64"/>
@@ -16510,13 +16515,13 @@
         <v>49</v>
       </c>
       <c r="C281" s="62" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D281" s="61" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="E281" s="63" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="F281" s="64"/>
       <c r="G281" s="64"/>
@@ -16551,13 +16556,13 @@
         <v>49</v>
       </c>
       <c r="C282" s="62" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D282" s="61" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E282" s="63" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F282" s="64"/>
       <c r="G282" s="64"/>
@@ -16592,13 +16597,13 @@
         <v>49</v>
       </c>
       <c r="C283" s="62" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D283" s="61" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="E283" s="63" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="F283" s="64"/>
       <c r="G283" s="64"/>
@@ -16633,10 +16638,10 @@
         <v>49</v>
       </c>
       <c r="C284" s="62" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D284" s="61" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="E284" s="63" t="s">
         <v>80</v>
@@ -16674,10 +16679,10 @@
         <v>49</v>
       </c>
       <c r="C285" s="62" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D285" s="61" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="E285" s="63" t="s">
         <v>90</v>
@@ -19421,42 +19426,42 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
   </sheetData>
@@ -19494,22 +19499,22 @@
   <sheetData>
     <row r="1" spans="1:7" customHeight="1" ht="14.25">
       <c r="A1" s="26" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D1" s="72" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="G1" s="39" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="2" spans="1:7" customHeight="1" ht="14.25">
@@ -19517,13 +19522,13 @@
         <v>50</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C2" s="70" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D2" s="73" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="3" spans="1:7" customHeight="1" ht="14.25">
@@ -19531,13 +19536,13 @@
         <v>59</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C3" s="70" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="D3" s="74" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="4" spans="1:7" customHeight="1" ht="14.25">
@@ -19545,13 +19550,13 @@
         <v>63</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C4" s="70" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="D4" s="75" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="5" spans="1:7" customHeight="1" ht="14.25">
@@ -19559,13 +19564,13 @@
         <v>73</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C5" s="70" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="D5" s="74" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="6" spans="1:7" customHeight="1" ht="14.25">
@@ -19573,13 +19578,13 @@
         <v>75</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C6" s="70" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D6" s="75" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="7" spans="1:7" customHeight="1" ht="14.5">
@@ -19587,13 +19592,13 @@
         <v>77</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C7" s="70" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D7" s="75" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="8" spans="1:7" customHeight="1" ht="14.5">
@@ -19601,13 +19606,13 @@
         <v>65</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C8" s="70" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="D8" s="75" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="9" spans="1:7" customHeight="1" ht="14.5">
@@ -19615,125 +19620,125 @@
         <v>61</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C9" s="70" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D9" s="75" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="10" spans="1:7" customHeight="1" ht="43.5">
       <c r="A10" s="5" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C10" s="71" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="D10" s="74" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="11" spans="1:7" customHeight="1" ht="14.25">
       <c r="A11" s="5" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C11" s="70" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D11" s="75" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="12" spans="1:7" customHeight="1" ht="14.25">
       <c r="A12" s="5" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C12" s="70" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D12" s="75" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="13" spans="1:7" customHeight="1" ht="14.25">
       <c r="A13" s="5" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C13" s="70" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="D13" s="75" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="14" spans="1:7" customHeight="1" ht="14.25">
       <c r="A14" s="5" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C14" s="70" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D14" s="75" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="15" spans="1:7" customHeight="1" ht="14.25">
       <c r="A15" s="5" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C15" s="70">
         <v>521</v>
       </c>
       <c r="D15" s="75" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="16" spans="1:7" customHeight="1" ht="14.25">
       <c r="A16" s="77" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C16" s="79" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D16" s="75" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="17" spans="1:7" customHeight="1" ht="14.25">
       <c r="A17" s="78" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B17" s="76" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C17" s="80" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D17" s="75" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="18" spans="1:7" customHeight="1" ht="14.25"/>
@@ -20722,7 +20727,7 @@
     </row>
     <row r="2" spans="1:6" customHeight="1" ht="14.25">
       <c r="A2" s="4" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>70</v>
@@ -20730,7 +20735,7 @@
     </row>
     <row r="3" spans="1:6" customHeight="1" ht="14.25">
       <c r="A3" s="4" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>53</v>
